--- a/tame_output/ON/bt/strategyON_20240710.xlsx
+++ b/tame_output/ON/bt/strategyON_20240710.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>13.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>122.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.0%</t>
+          <t>-49.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.9%</t>
+          <t>-68.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.4%</t>
+          <t>452.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-502.2%</t>
+          <t>-501.1%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>478.4%</t>
+          <t>481.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.9%</t>
+          <t>-155.5%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-124.9%</t>
+          <t>-125.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.966367958250078</v>
+        <v>-9.017105163921823</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.4201080987483454</v>
+        <v>-0.4404029810170429</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.941065540207365</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.868460919573588</v>
+        <v>-8.919198125245332</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3812455982512097</v>
+        <v>-0.4015404805199076</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.873079790346809</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.84450737859763</v>
+        <v>-8.895244584269374</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3709956757153332</v>
+        <v>-0.3912905579840307</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.849126249370851</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.580447440274833</v>
+        <v>-8.631184645946577</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2786320165479665</v>
+        <v>-0.2989268988166645</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.585066311048055</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.873367816769995</v>
+        <v>-7.924105022441739</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.00141279919366788</v>
+        <v>-0.01888208307503003</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.585066311048055</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.833183518403804</v>
+        <v>-7.883920724075549</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.01783014242798542</v>
+        <v>-0.002464739840712493</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.544882012681864</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.669783647464442</v>
+        <v>-7.720520853136186</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.08255691202448734</v>
+        <v>0.06226202975578943</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.381482141742502</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.436302425234843</v>
+        <v>-7.487039630906588</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1838738297541793</v>
+        <v>0.1635789474854814</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.148000919512903</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.286636034227328</v>
+        <v>-7.337373239899073</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.240848175844226</v>
+        <v>0.2205532935755281</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.055097428270367</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.154360560596442</v>
+        <v>-7.205097766268186</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2891258520436075</v>
+        <v>0.2688309697749101</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.9228219546394807</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.9986222280367</v>
+        <v>-7.049359433708444</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3542362457551409</v>
+        <v>0.3339413634864434</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.7670836220797391</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.749622429353119</v>
+        <v>-6.800359635024863</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4667425064522321</v>
+        <v>0.4464476241835347</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.7670836220797391</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.855212419126223</v>
+        <v>-6.905949624797968</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2965305809437719</v>
+        <v>0.276235698675074</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.8726736118528435</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.87394732124482</v>
+        <v>-6.924684526916565</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3375809619734191</v>
+        <v>0.3172860797047217</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.8782696215129748</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.726007279837221</v>
+        <v>-6.776744485508965</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2768780558482913</v>
+        <v>0.2565831735795938</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.8579487056044173</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.673037757583232</v>
+        <v>-6.723774963254977</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2893518784964089</v>
+        <v>0.269056996227711</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.8049791833504284</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.629489350812542</v>
+        <v>-6.680226556484286</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2998106291095919</v>
+        <v>0.279515746840894</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.8049791833504284</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.387340957358684</v>
+        <v>-6.438078163030428</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.4111323408722782</v>
+        <v>0.3908374586035803</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.8049791833504284</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.279081820236162</v>
+        <v>-6.329819025907907</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4489681161804819</v>
+        <v>0.428673233911784</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.8049791833504284</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.155790685419031</v>
+        <v>-6.206527891090776</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4957826641179111</v>
+        <v>0.4754877818492131</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.6816880485332979</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.134641486515588</v>
+        <v>-6.185378692187332</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5119433219166134</v>
+        <v>0.4916484396479159</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.6605388496298545</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.890876044532144</v>
+        <v>-5.941613250203888</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6052302070570419</v>
+        <v>0.5849353247883444</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.6605388496298545</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.789113224254849</v>
+        <v>-5.839850429926593</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6480596490879758</v>
+        <v>0.6277647668192783</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.6473197812374258</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.539262830305774</v>
+        <v>-5.590000035977519</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7407418816513078</v>
+        <v>0.7204469993826104</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.6473197812374258</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.363370737838341</v>
+        <v>-5.414107943510086</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8146978421589299</v>
+        <v>0.794402959890232</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.6473197812374258</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.191924274815878</v>
+        <v>-5.242661480487622</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8966039334224689</v>
+        <v>0.876309051153771</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.4758733182149627</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.117634709077539</v>
+        <v>-5.168371914749283</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9253402373341015</v>
+        <v>0.9050453550654036</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.4015837524766234</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.053998966843604</v>
+        <v>-5.104736172515349</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9554893352819924</v>
+        <v>0.935194453013295</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.3379480102426889</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.942572207517684</v>
+        <v>-4.993309413189428</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9812542977961562</v>
+        <v>0.9609594155274586</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.3379480102426889</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.702141710712824</v>
+        <v>-4.752878916384568</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.079169573142978</v>
+        <v>1.05887469087428</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.09751751343782861</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.629899142541629</v>
+        <v>-4.680636348213373</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.111995914246276</v>
+        <v>1.091701031977578</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.09751751343782861</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.576900820260241</v>
+        <v>-4.627638025931986</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.133873827076171</v>
+        <v>1.113578944807473</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.04218125443588977</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.468095934780514</v>
+        <v>-4.518833140452259</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.174393852488055</v>
+        <v>1.154098970219358</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.04218125443588977</v>
@@ -45918,10 +45918,10 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.248075136743504</v>
+        <v>-4.298812342415248</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.263981208713474</v>
+        <v>1.243686326444776</v>
       </c>
       <c r="F1929" t="n">
         <v>0.09903859063209047</v>
@@ -45941,10 +45941,10 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.115207447680226</v>
+        <v>-4.16594465335197</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.333022467140608</v>
+        <v>1.31272758487191</v>
       </c>
       <c r="F1930" t="n">
         <v>0.09903859063209047</v>
@@ -45964,10 +45964,10 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.995034364315727</v>
+        <v>-4.045771569987472</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.382237544926709</v>
+        <v>1.361942662658012</v>
       </c>
       <c r="F1931" t="n">
         <v>0.2192116739965894</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.85036221921599</v>
+        <v>-3.901099424887734</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.450194505528044</v>
+        <v>1.429899623259347</v>
       </c>
       <c r="F1932" t="n">
         <v>0.3638838190963268</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.910237046573682</v>
+        <v>-3.960974252245427</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.412282065986393</v>
+        <v>1.391987183717695</v>
       </c>
       <c r="F1933" t="n">
         <v>0.3040089917386347</v>
@@ -46033,10 +46033,10 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.790416815662845</v>
+        <v>-3.841154021334589</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.475499327584937</v>
+        <v>1.455204445316239</v>
       </c>
       <c r="F1934" t="n">
         <v>0.3040089917386347</v>
@@ -46056,10 +46056,10 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.792886522124651</v>
+        <v>-3.843623727796395</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.382155644322656</v>
+        <v>1.361860762053958</v>
       </c>
       <c r="F1935" t="n">
         <v>0.3015392852768286</v>
@@ -46079,10 +46079,10 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.861256708448661</v>
+        <v>-3.911993914120405</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.274069431278353</v>
+        <v>1.253774549009655</v>
       </c>
       <c r="F1936" t="n">
         <v>0.3108149843130435</v>
@@ -46102,10 +46102,10 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.875044761295707</v>
+        <v>-3.925781966967452</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.258990918771426</v>
+        <v>1.238696036502728</v>
       </c>
       <c r="F1937" t="n">
         <v>0.3108149843130435</v>
@@ -46125,10 +46125,10 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.906037920624413</v>
+        <v>-3.956775126296157</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.071303220080331</v>
+        <v>1.051008337811633</v>
       </c>
       <c r="F1938" t="n">
         <v>0.3108149843130435</v>
@@ -46148,10 +46148,10 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.730563660831943</v>
+        <v>-3.781300866503688</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.146060155989106</v>
+        <v>1.125765273720408</v>
       </c>
       <c r="F1939" t="n">
         <v>0.3108149843130435</v>
@@ -46171,10 +46171,10 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.841499913473192</v>
+        <v>-3.892237119144936</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.077427683693814</v>
+        <v>1.057132801425116</v>
       </c>
       <c r="F1940" t="n">
         <v>0.3108149843130435</v>
@@ -46194,10 +46194,10 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.80783636800091</v>
+        <v>-3.858573573672655</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.094024487102632</v>
+        <v>1.073729604833934</v>
       </c>
       <c r="F1941" t="n">
         <v>0.3444785297853253</v>
@@ -46217,10 +46217,10 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.747983748797187</v>
+        <v>-3.798720954468931</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.128137921216254</v>
+        <v>1.107843038947556</v>
       </c>
       <c r="F1942" t="n">
         <v>0.3444785297853253</v>
@@ -46240,10 +46240,10 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.66174028577081</v>
+        <v>-3.712477491442554</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.157581577000665</v>
+        <v>1.137286694731967</v>
       </c>
       <c r="F1943" t="n">
         <v>0.3444785297853253</v>
@@ -46263,10 +46263,10 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.70704710516979</v>
+        <v>-3.757784310841534</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.131234624685598</v>
+        <v>1.110939742416901</v>
       </c>
       <c r="F1944" t="n">
         <v>0.3036683667760945</v>
@@ -46286,10 +46286,10 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.736080209872091</v>
+        <v>-3.786817415543835</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.120173255837779</v>
+        <v>1.099878373569082</v>
       </c>
       <c r="F1945" t="n">
         <v>0.3036683667760945</v>
@@ -46309,10 +46309,10 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.643269728421232</v>
+        <v>-3.694006934092976</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.086570140309489</v>
+        <v>1.066275258040791</v>
       </c>
       <c r="F1946" t="n">
         <v>0.3964788482269539</v>
@@ -46332,10 +46332,10 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.687659197750659</v>
+        <v>-3.738396403422404</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.070687828502318</v>
+        <v>1.050392946233621</v>
       </c>
       <c r="F1947" t="n">
         <v>0.3520893788975262</v>
@@ -46355,10 +46355,10 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.574987979514409</v>
+        <v>-3.625725185186154</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.110832024308542</v>
+        <v>1.090537142039844</v>
       </c>
       <c r="F1948" t="n">
         <v>0.4647605971337764</v>
@@ -46378,10 +46378,10 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.462610978331737</v>
+        <v>-3.513348184003481</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.161274120612278</v>
+        <v>1.14097923834358</v>
       </c>
       <c r="F1949" t="n">
         <v>0.4647605971337764</v>
@@ -46401,10 +46401,10 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.49039137623309</v>
+        <v>-3.541128581904834</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.161659163220276</v>
+        <v>1.141364280951578</v>
       </c>
       <c r="F1950" t="n">
         <v>0.4369801992324234</v>
@@ -46424,10 +46424,10 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.573392657258369</v>
+        <v>-3.624129862930113</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9668143708108174</v>
+        <v>0.9465194885421195</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4184093147052496</v>
@@ -46447,10 +46447,10 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.6820067357017</v>
+        <v>-3.732743941373444</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.04351840015269</v>
+        <v>1.023223517883993</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4184093147052496</v>
@@ -46470,10 +46470,10 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.646597697453557</v>
+        <v>-3.697334903125301</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.072195041554271</v>
+        <v>1.051900159285573</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4184093147052496</v>
@@ -46493,10 +46493,10 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.608214034895406</v>
+        <v>-3.65895124056715</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.0849679479199</v>
+        <v>1.064673065651202</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4567929772634008</v>
@@ -46516,10 +46516,10 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.43109770486024</v>
+        <v>-3.481834910531984</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.152543508779269</v>
+        <v>1.132248626510571</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4567929772634008</v>
@@ -46539,10 +46539,10 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.476189949693786</v>
+        <v>-3.52692715536553</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.135190002607763</v>
+        <v>1.114895120339066</v>
       </c>
       <c r="F1956" t="n">
         <v>0.394896934094011</v>
@@ -46562,10 +46562,10 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.296814528455018</v>
+        <v>-3.347551734126762</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.200727146409685</v>
+        <v>1.180432264140987</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5516736922647296</v>
@@ -46585,10 +46585,10 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.341828741975624</v>
+        <v>-3.392565947647368</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.163528916333032</v>
+        <v>1.143234034064334</v>
       </c>
       <c r="F1958" t="n">
         <v>0.521324796950125</v>
@@ -46608,10 +46608,10 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.60883325224806</v>
+        <v>-3.659570457919804</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.062418674563004</v>
+        <v>1.042123792294306</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3269617589071764</v>
@@ -46631,10 +46631,10 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.710031033685232</v>
+        <v>-3.760768239356977</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.021143483884636</v>
+        <v>1.000848601615938</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2585529453618572</v>
@@ -46654,10 +46654,10 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.70352006707092</v>
+        <v>-3.754257272742664</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.021347832084678</v>
+        <v>1.00105294981598</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2585529453618572</v>
@@ -46677,10 +46677,10 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.684481939363622</v>
+        <v>-3.735219145035367</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.025487802375842</v>
+        <v>1.005192920107144</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2003693340306627</v>
@@ -46700,10 +46700,10 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.71560857051424</v>
+        <v>-3.766345776185985</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.190619018854275</v>
+        <v>1.170324136585577</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2003693340306627</v>
@@ -46723,10 +46723,10 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.729475331848158</v>
+        <v>-3.780212537519902</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.185905643306842</v>
+        <v>1.165610761038144</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1625114172968398</v>
@@ -46746,10 +46746,10 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.684671160308228</v>
+        <v>-3.735408365979972</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.20983584231974</v>
+        <v>1.189540960051042</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1625114172968398</v>
@@ -46769,10 +46769,10 @@
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.536928190073226</v>
+        <v>-3.58766539574497</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.16688325169094</v>
+        <v>1.146588369422242</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3303187745317229</v>
@@ -46792,10 +46792,10 @@
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.638942872604447</v>
+        <v>-3.689680078276191</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.128871000209932</v>
+        <v>1.108576117941235</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3303187745317229</v>
@@ -46815,10 +46815,10 @@
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.632790166551662</v>
+        <v>-3.683527372223407</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.131994431022705</v>
+        <v>1.111699548754007</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3364714805845072</v>
@@ -46838,10 +46838,10 @@
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.649599464702164</v>
+        <v>-3.700336670373908</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.124351188502614</v>
+        <v>1.104056306233916</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3196621824340056</v>
@@ -46861,10 +46861,10 @@
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.587301465926042</v>
+        <v>-3.638038671597786</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.215605941809884</v>
+        <v>1.195311059541186</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3196621824340056</v>
@@ -46884,10 +46884,10 @@
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.385511268260884</v>
+        <v>-3.436248473932628</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.098614022590074</v>
+        <v>1.078319140321376</v>
       </c>
       <c r="F1971" t="n">
         <v>0.51768037460316</v>
@@ -46907,10 +46907,10 @@
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.312133171172147</v>
+        <v>-3.362870376843892</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.198255493747744</v>
+        <v>1.177960611479046</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5910584716918965</v>
@@ -46930,10 +46930,10 @@
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.409873715797122</v>
+        <v>-3.460610921468866</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.173787012013798</v>
+        <v>1.1534921297451</v>
       </c>
       <c r="F1973" t="n">
         <v>0.5751691935589163</v>
@@ -46953,10 +46953,10 @@
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.586211475920051</v>
+        <v>-3.636948681591795</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.101787888789298</v>
+        <v>1.0814930065206</v>
       </c>
       <c r="F1974" t="n">
         <v>0.3988314334359869</v>
@@ -46976,10 +46976,10 @@
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.509789429488124</v>
+        <v>-3.560526635159869</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.130848325401997</v>
+        <v>1.110553443133299</v>
       </c>
       <c r="F1975" t="n">
         <v>0.3988314334359869</v>
@@ -46999,10 +46999,10 @@
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.465416297849556</v>
+        <v>-3.5161535035213</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.148460445492861</v>
+        <v>1.128165563224163</v>
       </c>
       <c r="F1976" t="n">
         <v>0.4432045650745555</v>
@@ -47022,10 +47022,10 @@
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.342582076962388</v>
+        <v>-3.393319282634133</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.191987927986318</v>
+        <v>1.17169304571762</v>
       </c>
       <c r="F1977" t="n">
         <v>0.4432045650745555</v>
@@ -47045,10 +47045,10 @@
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.294926346401333</v>
+        <v>-3.345663552073077</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.217431977238545</v>
+        <v>1.197137094969847</v>
       </c>
       <c r="F1978" t="n">
         <v>0.4908602956356112</v>
@@ -47068,10 +47068,10 @@
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.194408187902578</v>
+        <v>-3.245145393574322</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.262531614012772</v>
+        <v>1.242236731744074</v>
       </c>
       <c r="F1979" t="n">
         <v>0.5913784541343657</v>
@@ -47091,10 +47091,10 @@
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.255074778304967</v>
+        <v>-3.305811983976711</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.225019650327688</v>
+        <v>1.204724768058991</v>
       </c>
       <c r="F1980" t="n">
         <v>0.5096801374158321</v>
@@ -47114,10 +47114,10 @@
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.210236376696569</v>
+        <v>-3.260973582368313</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.247052713581676</v>
+        <v>1.226757831312978</v>
       </c>
       <c r="F1981" t="n">
         <v>0.5142235703607015</v>
@@ -47137,10 +47137,10 @@
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.310995012453568</v>
+        <v>-3.361732218125312</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.210910198909955</v>
+        <v>1.190615316641257</v>
       </c>
       <c r="F1982" t="n">
         <v>0.4253980016336961</v>
@@ -47160,10 +47160,10 @@
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.266792175367667</v>
+        <v>-3.317529381039412</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.234470936272152</v>
+        <v>1.214176054003454</v>
       </c>
       <c r="F1983" t="n">
         <v>0.4696008387195966</v>
@@ -47183,10 +47183,10 @@
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.30377120303111</v>
+        <v>-3.354508408702855</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.218089325676022</v>
+        <v>1.197794443407324</v>
       </c>
       <c r="F1984" t="n">
         <v>0.5065747405109271</v>
@@ -47206,10 +47206,10 @@
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.145479785491838</v>
+        <v>-3.196216991163582</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.332653657874771</v>
+        <v>1.312358775606073</v>
       </c>
       <c r="F1985" t="n">
         <v>0.5065747405109271</v>
@@ -47229,10 +47229,10 @@
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.937837781857362</v>
+        <v>-2.988574987529106</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.414151163922814</v>
+        <v>1.393856281654117</v>
       </c>
       <c r="F1986" t="n">
         <v>0.7142167441454033</v>
@@ -47252,10 +47252,10 @@
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.886805689134834</v>
+        <v>-2.937542894806578</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.429512229250096</v>
+        <v>1.409217346981398</v>
       </c>
       <c r="F1987" t="n">
         <v>0.7652488368679312</v>
@@ -47275,10 +47275,10 @@
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.821581508007628</v>
+        <v>-2.872318713679372</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.472789305793683</v>
+        <v>1.452494423524985</v>
       </c>
       <c r="F1988" t="n">
         <v>0.8304730179951368</v>
@@ -47298,10 +47298,10 @@
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.784154487936494</v>
+        <v>-2.834891693608239</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.483721086121417</v>
+        <v>1.463426203852719</v>
       </c>
       <c r="F1989" t="n">
         <v>0.8357245560243185</v>
@@ -47321,10 +47321,10 @@
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.804266143971203</v>
+        <v>-2.855003349642947</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.476933216038774</v>
+        <v>1.456638333770076</v>
       </c>
       <c r="F1990" t="n">
         <v>0.8467519010217377</v>
@@ -47344,10 +47344,10 @@
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.750521329543998</v>
+        <v>-2.801258535215742</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.658988912830866</v>
+        <v>1.638694030562169</v>
       </c>
       <c r="F1991" t="n">
         <v>0.8568152104621997</v>
@@ -47367,10 +47367,10 @@
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.726729760937856</v>
+        <v>-2.7774669666096</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.788618449491141</v>
+        <v>1.768323567222443</v>
       </c>
       <c r="F1992" t="n">
         <v>0.8806067790683419</v>
@@ -47390,10 +47390,10 @@
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.700645676674048</v>
+        <v>-2.751382882345792</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.790760059210523</v>
+        <v>1.770465176941825</v>
       </c>
       <c r="F1993" t="n">
         <v>0.8806067790683419</v>
@@ -47413,10 +47413,10 @@
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.622514495825101</v>
+        <v>-2.673251701496845</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.820205727133881</v>
+        <v>1.799910844865183</v>
       </c>
       <c r="F1994" t="n">
         <v>0.9547835899520265</v>
@@ -47436,10 +47436,10 @@
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.613622034431818</v>
+        <v>-2.664359240103562</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.841317117417985</v>
+        <v>1.821022235149288</v>
       </c>
       <c r="F1995" t="n">
         <v>0.9547835899520265</v>
@@ -47459,10 +47459,10 @@
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.782098151401696</v>
+        <v>-2.83283535707344</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.765781718034618</v>
+        <v>1.745486835765921</v>
       </c>
       <c r="F1996" t="n">
         <v>0.9268357542354457</v>
@@ -47482,10 +47482,10 @@
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.084298622540112</v>
+        <v>-2.135035828211857</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.026171226767113</v>
+        <v>2.005876344498416</v>
       </c>
       <c r="F1997" t="n">
         <v>0.8564876948650351</v>
@@ -47505,10 +47505,10 @@
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.06157751885696</v>
+        <v>-2.112314724528704</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.025923690737279</v>
+        <v>2.005628808468581</v>
       </c>
       <c r="F1998" t="n">
         <v>0.8564876948650351</v>
@@ -47528,10 +47528,10 @@
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.059852475566916</v>
+        <v>-2.11058968123866</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.185519833904466</v>
+        <v>2.165224951635768</v>
       </c>
       <c r="F1999" t="n">
         <v>0.8582127381550788</v>
@@ -47551,10 +47551,10 @@
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.214633482345171</v>
+        <v>-2.265370688016915</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.16068525368681</v>
+        <v>2.140390371418112</v>
       </c>
       <c r="F2000" t="n">
         <v>0.8248450641006027</v>
@@ -47574,10 +47574,10 @@
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.163198148960511</v>
+        <v>-2.213935354632256</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.177934743030219</v>
+        <v>2.157639860761521</v>
       </c>
       <c r="F2001" t="n">
         <v>0.8762803974852623</v>
@@ -47597,10 +47597,10 @@
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.136246924634023</v>
+        <v>-2.186984130305768</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.198721386405556</v>
+        <v>2.178426504136858</v>
       </c>
       <c r="F2002" t="n">
         <v>0.8911607435129815</v>
@@ -47620,10 +47620,10 @@
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.27219993269034</v>
+        <v>-2.322937138362084</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.328443315327989</v>
+        <v>2.308148433059292</v>
       </c>
       <c r="F2003" t="n">
         <v>0.8911607435129815</v>
@@ -47643,10 +47643,10 @@
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.294608050495212</v>
+        <v>-2.345345256166956</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.311596763109034</v>
+        <v>2.291301880840336</v>
       </c>
       <c r="F2004" t="n">
         <v>0.8911607435129815</v>
@@ -47666,10 +47666,10 @@
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.442613817974611</v>
+        <v>-2.493351023646356</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.254448455666911</v>
+        <v>2.234153573398213</v>
       </c>
       <c r="F2005" t="n">
         <v>0.80443373464944</v>
@@ -47689,10 +47689,10 @@
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.452054743863141</v>
+        <v>-2.502791949534886</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.306925803033346</v>
+        <v>2.286630920764648</v>
       </c>
       <c r="F2006" t="n">
         <v>0.9268608521928314</v>
@@ -47712,10 +47712,10 @@
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.450767980323585</v>
+        <v>-2.501505185995329</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.31033160299447</v>
+        <v>2.290036720725772</v>
       </c>
       <c r="F2007" t="n">
         <v>0.928147615732388</v>
@@ -47735,10 +47735,10 @@
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.452325034312876</v>
+        <v>-2.503062239984621</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.307820594292529</v>
+        <v>2.287525712023831</v>
       </c>
       <c r="F2008" t="n">
         <v>0.928147615732388</v>
@@ -47758,10 +47758,10 @@
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.459596919836341</v>
+        <v>-2.510334125508085</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.299732069686005</v>
+        <v>2.279437187417307</v>
       </c>
       <c r="F2009" t="n">
         <v>0.9208757302089232</v>
@@ -47781,10 +47781,10 @@
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.45775590077809</v>
+        <v>-2.508493106449834</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.298902487519458</v>
+        <v>2.27860760525076</v>
       </c>
       <c r="F2010" t="n">
         <v>0.9221439568803916</v>
@@ -47804,10 +47804,10 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.46466460627777</v>
+        <v>-2.515401811949515</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.309212412185504</v>
+        <v>2.288917529916806</v>
       </c>
       <c r="F2011" t="n">
         <v>0.9221439568803916</v>
@@ -47827,10 +47827,10 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.46622624909263</v>
+        <v>-2.516963454764374</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.30858775505956</v>
+        <v>2.288292872790862</v>
       </c>
       <c r="F2012" t="n">
         <v>0.9221439568803916</v>
@@ -47850,10 +47850,10 @@
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.494127036202103</v>
+        <v>-2.544864241873847</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.295951481342773</v>
+        <v>2.275656599074075</v>
       </c>
       <c r="F2013" t="n">
         <v>0.8875470327374568</v>
@@ -47873,10 +47873,10 @@
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.497160033714777</v>
+        <v>-2.547897239386521</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.291502726314902</v>
+        <v>2.271207844046204</v>
       </c>
       <c r="F2014" t="n">
         <v>0.8845140352247829</v>
@@ -47896,10 +47896,10 @@
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.517221354991284</v>
+        <v>-2.567958560663028</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.350184157394803</v>
+        <v>2.329889275126106</v>
       </c>
       <c r="F2015" t="n">
         <v>0.8644527139482758</v>
@@ -47919,10 +47919,10 @@
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.773942172986108</v>
+        <v>-2.824679378657852</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.387807549198721</v>
+        <v>2.367512666930023</v>
       </c>
       <c r="F2016" t="n">
         <v>0.756038139804461</v>
@@ -47942,10 +47942,10 @@
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.927928590762248</v>
+        <v>-2.978665796433992</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.395193251233904</v>
+        <v>2.374898368965206</v>
       </c>
       <c r="F2017" t="n">
         <v>0.756038139804461</v>
@@ -47965,10 +47965,10 @@
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.877406686934582</v>
+        <v>-2.928143892606327</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.401453214885091</v>
+        <v>2.381158332616394</v>
       </c>
       <c r="F2018" t="n">
         <v>0.756038139804461</v>
@@ -47988,10 +47988,10 @@
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.129881840942307</v>
+        <v>-3.180619046614051</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.312333642337415</v>
+        <v>2.292038760068718</v>
       </c>
       <c r="F2019" t="n">
         <v>0.756038139804461</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.812126769436484</v>
+        <v>3.412009466788656</v>
       </c>
       <c r="C2020" t="n">
         <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.405996585455989</v>
+        <v>-3.394981915841852</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.203098279050886</v>
+        <v>2.207504146896541</v>
       </c>
       <c r="F2020" t="n">
         <v>0.756038139804461</v>

--- a/tame_output/ON/bt/strategyON_20240710.xlsx
+++ b/tame_output/ON/bt/strategyON_20240710.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.7%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-49.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.2%</t>
+          <t>-68.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.9%</t>
+          <t>452.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-501.1%</t>
+          <t>-506.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-35.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.5%</t>
+          <t>-157.7%</t>
         </is>
       </c>
     </row>
@@ -48011,10 +48011,10 @@
         <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.394981915841852</v>
+        <v>-3.450091848535759</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.207504146896541</v>
+        <v>2.185460173818978</v>
       </c>
       <c r="F2020" t="n">
         <v>0.756038139804461</v>

--- a/tame_output/ON/bt/strategyON_20240710.xlsx
+++ b/tame_output/ON/bt/strategyON_20240710.xlsx
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.617515458616743</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.627687845048876</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.622634115622736</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.614409891067262</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.614961764100363</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.544234455991729</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.54610793191633</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.541183640428053</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.54667493625872</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.558172138027259</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.396527858027912</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.519809382105439</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.500616837437029</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.506308399775975</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.505512321672476</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.503112283226793</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.499637002435038</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677218871373718</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678052200359852</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.582010952033977</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.584804573565458</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.585466921957117</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.584547398697227</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.650882952494048</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.453174954208175</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.52346518653035</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.538092922646394</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.536628903471065</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.535120521510994</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.53498338894643</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.529377183085021</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.535758940112825</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.54065131348755</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.527405985963422</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.531503688574051</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
         <v>2.535664628205129</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.541544230732966</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.539954231202214</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.591201996385253</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.589642700979506</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.584590929217776</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.601778333310481</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.597739305609762</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.598996097941002</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.759553868962213</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>2.87966677818003</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>2.871374754193889</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.869567949777668</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.88712235550446</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.878977402909044</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.860247100096906</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.85091112259381</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.009817248444979</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.046895070938626</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
         <v>3.043570426928171</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.053576580572912</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.237679712717872</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
         <v>3.229796407620865</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.231850407170503</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
         <v>3.28810412489235</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
         <v>3.290995219437651</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
         <v>3.289107032331426</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.283927261934288</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.282361272144441</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647107</v>
       </c>
       <c r="C2011" t="n">
         <v>3.295434679010359</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.749896851763533</v>
       </c>
       <c r="C2012" t="n">
         <v>3.295434679010359</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392117</v>
       </c>
       <c r="C2013" t="n">
         <v>3.293958720137361</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172528</v>
       </c>
       <c r="C2014" t="n">
         <v>3.29072316411456</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971079</v>
+        <v>3.619362241971081</v>
       </c>
       <c r="C2015" t="n">
         <v>3.357429123705064</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199807</v>
       </c>
       <c r="C2016" t="n">
         <v>3.497740842706911</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622238</v>
       </c>
       <c r="C2017" t="n">
         <v>3.566721111852551</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808529</v>
+        <v>3.619937176808531</v>
       </c>
       <c r="C2018" t="n">
         <v>3.552772313972671</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994894</v>
+        <v>3.656346893994896</v>
       </c>
       <c r="C2019" t="n">
         <v>3.564642803028085</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.412009466788656</v>
+        <v>3.412009466788657</v>
       </c>
       <c r="C2020" t="n">
         <v>3.565853337547029</v>

--- a/tame_output/ON/bt/strategyON_20240710.xlsx
+++ b/tame_output/ON/bt/strategyON_20240710.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,27 +849,27 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.7%</t>
+          <t>-68.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.9%</t>
+          <t>-26.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-44.1%</t>
+          <t>-101.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2020"/>
+  <dimension ref="A1:G2021"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.617515458616743</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.627687845048876</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.622634115622736</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.614409891067262</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.614961764100363</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.544234455991729</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.54610793191633</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.541183640428053</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.54667493625872</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.558172138027259</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.396527858027912</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.519809382105439</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.500616837437029</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.506308399775975</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.505512321672476</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.503112283226793</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.499637002435038</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677218871373718</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678052200359852</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.582010952033977</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.584804573565458</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.585466921957117</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.584547398697227</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.650882952494048</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.453174954208175</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.52346518653035</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.538092922646394</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.536628903471065</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.535120521510994</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.53498338894643</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.529377183085021</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.535758940112825</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.54065131348755</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
         <v>2.527405985963422</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.531503688574051</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.535664628205129</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.541544230732966</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.539954231202214</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.591201996385253</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.589642700979506</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.584590929217776</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.601778333310481</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.597739305609762</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.598996097941002</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.759553868962213</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.87966677818003</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.871374754193889</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.869567949777668</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.88712235550446</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.878977402909044</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.860247100096906</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>2.85091112259381</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.009817248444979</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.046895070938626</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.043570426928171</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.053576580572912</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.237679712717872</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714426</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.229796407620865</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.231850407170503</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.28810412489235</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.290995219437651</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347704</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.289107032331426</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.283927261934288</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.282361272144441</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647107</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.295434679010359</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763533</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.295434679010359</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392117</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.293958720137361</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172528</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.29072316411456</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971081</v>
+        <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
         <v>3.357429123705064</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199807</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
         <v>3.497740842706911</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622238</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
         <v>3.566721111852551</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808531</v>
+        <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
         <v>3.552772313972671</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994896</v>
+        <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
         <v>3.564642803028085</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.412009466788657</v>
+        <v>3.674042696358299</v>
       </c>
       <c r="C2020" t="n">
         <v>3.565853337547029</v>
@@ -48021,6 +48021,29 @@
       </c>
       <c r="G2020" t="n">
         <v>4.019476221429706</v>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" s="2" t="n">
+        <v>45483</v>
+      </c>
+      <c r="B2021" t="n">
+        <v>3.416565728328048</v>
+      </c>
+      <c r="C2021" t="n">
+        <v>3.455089829280599</v>
+      </c>
+      <c r="D2021" t="n">
+        <v>-3.450091848535759</v>
+      </c>
+      <c r="E2021" t="n">
+        <v>2.185460173818978</v>
+      </c>
+      <c r="F2021" t="n">
+        <v>0.756038139804461</v>
+      </c>
+      <c r="G2021" t="n">
+        <v>3.448153626266967</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240710.xlsx
+++ b/tame_output/ON/bt/strategyON_20240710.xlsx
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.617515458616743</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.627687845048876</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.622634115622736</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.614409891067262</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.614961764100363</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.544234455991729</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.54610793191633</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.541183640428053</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.54667493625872</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.558172138027259</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.396527858027912</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.519809382105439</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.500616837437029</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.506308399775975</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.505512321672476</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.503112283226793</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.499637002435038</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677218871373718</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678052200359852</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.582010952033977</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.584804573565458</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.585466921957117</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.584547398697227</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.650882952494048</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.453174954208175</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.52346518653035</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.538092922646394</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.536628903471065</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.535120521510994</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.53498338894643</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.529377183085021</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.535758940112825</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.54065131348755</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.527405985963422</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.531503688574051</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
         <v>2.535664628205129</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.541544230732966</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.539954231202214</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.591201996385253</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.589642700979506</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.584590929217776</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
         <v>2.601778333310481</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.597739305609762</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.598996097941002</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.759553868962213</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>2.87966677818003</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>2.871374754193889</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.869567949777668</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.88712235550446</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.878977402909044</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.860247100096906</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.85091112259381</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.009817248444979</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.046895070938626</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
         <v>3.043570426928171</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.053576580572912</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.237679712717872</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
         <v>3.229796407620865</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.231850407170503</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
         <v>3.28810412489235</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
         <v>3.290995219437651</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
         <v>3.289107032331426</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.283927261934288</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.282361272144441</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647107</v>
       </c>
       <c r="C2011" t="n">
         <v>3.295434679010359</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.749896851763533</v>
       </c>
       <c r="C2012" t="n">
         <v>3.295434679010359</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392117</v>
       </c>
       <c r="C2013" t="n">
         <v>3.293958720137361</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172528</v>
       </c>
       <c r="C2014" t="n">
         <v>3.29072316411456</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971079</v>
+        <v>3.619362241971081</v>
       </c>
       <c r="C2015" t="n">
         <v>3.357429123705064</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199807</v>
       </c>
       <c r="C2016" t="n">
         <v>3.497740842706911</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622238</v>
       </c>
       <c r="C2017" t="n">
         <v>3.566721111852551</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808529</v>
+        <v>3.619937176808531</v>
       </c>
       <c r="C2018" t="n">
         <v>3.552772313972671</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994894</v>
+        <v>3.656346893994896</v>
       </c>
       <c r="C2019" t="n">
         <v>3.564642803028085</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358299</v>
+        <v>3.6740426963583</v>
       </c>
       <c r="C2020" t="n">
         <v>3.565853337547029</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.416565728328048</v>
+        <v>3.41656572832805</v>
       </c>
       <c r="C2021" t="n">
         <v>3.455089829280599</v>

--- a/tame_output/ON/bt/strategyON_20240710.xlsx
+++ b/tame_output/ON/bt/strategyON_20240710.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>57.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>83.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.6%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.4%</t>
+          <t>-70.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>108.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>121.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.9%</t>
+          <t>-48.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.0%</t>
+          <t>-65.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.7%</t>
+          <t>457.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.1%</t>
+          <t>-10.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-506.6%</t>
+          <t>-474.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-34.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>481.7%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.7%</t>
+          <t>-144.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-27.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-125.4%</t>
+          <t>-132.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-148.4%</t>
+          <t>-136.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,27 +1471,27 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.2%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-101.2%</t>
+          <t>-69.3%</t>
         </is>
       </c>
     </row>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.606854586351314</v>
+        <v>-5.334486617436109</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8735807170746397</v>
+        <v>0.982527904640722</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6809527638225534</v>
+        <v>-0.5596906225558451</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.708107317635381</v>
+        <v>2.780864602395406</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.015443363531993</v>
+        <v>-5.743075394616787</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7089067502171269</v>
+        <v>0.8178539377832097</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.089541541003232</v>
+        <v>-0.9682793997365235</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.461715595341733</v>
+        <v>2.534472880101758</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.292019463847826</v>
+        <v>-6.019651494932619</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.5934617425622548</v>
+        <v>0.7024089301283372</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.089541541003232</v>
+        <v>-0.9682793997365235</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.456901027813193</v>
+        <v>2.529658312573218</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.708411338134823</v>
+        <v>-6.436043369219616</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4248990434563331</v>
+        <v>0.5338462310224159</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.089541541003232</v>
+        <v>-0.9682793997365235</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.454895078422071</v>
+        <v>2.527652363182096</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.952682738861893</v>
+        <v>-6.680314769946686</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.3374491738341843</v>
+        <v>0.4463963614002671</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.089541541003232</v>
+        <v>-0.9682793997365235</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.46515376909075</v>
+        <v>2.537911053850775</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.157933758098653</v>
+        <v>-6.885565789183446</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2514483312851752</v>
+        <v>0.360395518851258</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.089541541003232</v>
+        <v>-0.9682793997365235</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.461253334236445</v>
+        <v>2.53401061899647</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.321513636283036</v>
+        <v>-7.04914566736783</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.1844213000664228</v>
+        <v>0.2933684876325056</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.089541541003232</v>
+        <v>-0.9682793997365235</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.459658254291446</v>
+        <v>2.532415539051471</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.618174978093234</v>
+        <v>-7.345807009178027</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.0695357392715521</v>
+        <v>0.1784829268376349</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.037022535470402</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.494948633540352</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.804894686402537</v>
+        <v>-7.53252671748733</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.009178448586572241</v>
+        <v>0.09976873897951055</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.037022535470402</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.490922329005949</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.187896075145167</v>
+        <v>-7.915528106229961</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.1624811054052082</v>
+        <v>-0.05353391783912587</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.037022535470402</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.490820227684365</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.369765866130201</v>
+        <v>-8.097397897214996</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.2326575058277922</v>
+        <v>-0.1237103182617099</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.340154467722146</v>
+        <v>-1.218892326455437</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.311512584304749</v>
+        <v>2.384269869064774</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.729296188634203</v>
+        <v>-8.456928219718998</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.3711193315313426</v>
+        <v>-0.2621721439652607</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.340154467722146</v>
+        <v>-1.218892326455437</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.316862887602799</v>
+        <v>2.389620172362824</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.779645252088425</v>
+        <v>-8.50727728317322</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.3833429369558536</v>
+        <v>-0.2743957493897717</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.390503531176368</v>
+        <v>-1.269241389909659</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.294569469487443</v>
+        <v>2.367326754247468</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.877264529509821</v>
+        <v>-8.604896560594616</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.4193488973026436</v>
+        <v>-0.3104017097365612</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.488122808597764</v>
+        <v>-1.366860667331056</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.239039653656374</v>
+        <v>2.311796938416399</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.024790617515464</v>
+        <v>-8.752422648600259</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.4754657761833285</v>
+        <v>-0.3665185886172462</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.635648896603408</v>
+        <v>-1.514386755336699</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.15341755717456</v>
+        <v>2.226174841934585</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.229048792845328</v>
+        <v>-8.956680823930123</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.5516558491966315</v>
+        <v>-0.4427086616305496</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.763287841217397</v>
+        <v>-1.642025699950688</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.082347387524809</v>
+        <v>2.155104672284834</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.262701631353801</v>
+        <v>-8.990333662438596</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.5606344301155848</v>
+        <v>-0.4516872425495029</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.863701209134434</v>
+        <v>-1.742439067867726</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.026581921259023</v>
+        <v>2.099339206019048</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.189231799686352</v>
+        <v>-8.916863830771147</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.5158747959551842</v>
+        <v>-0.4069276083891022</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.790231377466986</v>
+        <v>-1.668969236200277</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.086035521752913</v>
+        <v>2.158792806512938</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.364356217072896</v>
+        <v>-9.091988248157691</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.5713693421622845</v>
+        <v>-0.4624221545962026</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.965355794853529</v>
+        <v>-1.844093653586821</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.995516092068503</v>
+        <v>2.068273376828529</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.598808311087385</v>
+        <v>-9.32644034217218</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.6723693446696766</v>
+        <v>-0.5634221571035947</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.965355794853529</v>
+        <v>-1.844093653586821</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.988296927166908</v>
+        <v>2.061054211926932</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.703183042113832</v>
+        <v>-9.430815073198627</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.7207914278542313</v>
+        <v>-0.6118442402881494</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.069730525879975</v>
+        <v>-1.948468384613267</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.918999897777064</v>
+        <v>1.991757182537089</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.755969197714158</v>
+        <v>-9.483601228798953</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.7407901002558055</v>
+        <v>-0.6318429126897236</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.165406012462372</v>
+        <v>-2.044143871195664</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.862710395666182</v>
+        <v>1.935467680426207</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.882005991082448</v>
+        <v>-9.609638022167243</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.7885110889740066</v>
+        <v>-0.6795639014079247</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.14015438965263</v>
+        <v>-2.018892248385922</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.880555097981142</v>
+        <v>1.953312382741167</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.824934219186517</v>
+        <v>-9.552566250271312</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.7616920445292337</v>
+        <v>-0.6527448569631513</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.14015438965263</v>
+        <v>-2.018892248385922</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.884545433667543</v>
+        <v>1.957302718427568</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.966606060910637</v>
+        <v>-9.694238091995432</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.8198360081176235</v>
+        <v>-0.7108888205515411</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.14015438965263</v>
+        <v>-2.018892248385922</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.883070206768801</v>
+        <v>1.955827491528826</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.917015216485803</v>
+        <v>-9.644647247570598</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.7849462601828172</v>
+        <v>-0.6759990726167353</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.090563545227796</v>
+        <v>-1.969301403961088</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.927878123588574</v>
+        <v>2.000635408348598</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.768096882013946</v>
+        <v>-9.495728913098741</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.7384300600407578</v>
+        <v>-0.6294828724746755</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.059313954492623</v>
+        <v>-1.938051813225915</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.933576744382995</v>
+        <v>2.006334029143019</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.542251729294534</v>
+        <v>-9.269883760379329</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.6385129259167841</v>
+        <v>-0.5295657383507022</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.017387278905459</v>
+        <v>-1.896125137638751</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.968311822771502</v>
+        <v>2.041069107531526</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.417673072956942</v>
+        <v>-9.145305104041737</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.5875423188256885</v>
+        <v>-0.4785951312596066</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.017387278905459</v>
+        <v>-1.896125137638751</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.96945096732756</v>
+        <v>2.042208252087585</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.470568361001229</v>
+        <v>-9.198200392086024</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.6060666598812956</v>
+        <v>-0.4971194723152137</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.012431932817013</v>
+        <v>-1.891169791550305</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.975057949142736</v>
+        <v>2.047815233902761</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.398435185713348</v>
+        <v>-9.126067216798143</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.5714796855275068</v>
+        <v>-0.4625324979614245</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.012431932817013</v>
+        <v>-1.891169791550305</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.980791653381372</v>
+        <v>2.053548938141397</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.327068793103701</v>
+        <v>-9.054700824188496</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.552670390877513</v>
+        <v>-0.4437232033114311</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.941065540207365</v>
+        <v>-1.819803398940657</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.013874226553296</v>
+        <v>2.086631511313321</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.233609759118476</v>
+        <v>-8.961241790203271</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.5251702585963307</v>
+        <v>-0.4162230710302488</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.941065540207365</v>
+        <v>-1.819803398940657</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.003990745240388</v>
+        <v>2.076748030000413</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.017105163921823</v>
+        <v>-8.693999989334873</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.4404029810170429</v>
+        <v>-0.3111609111822635</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.941065540207365</v>
+        <v>-1.819803398940657</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.002156184741015</v>
+        <v>2.074913469501039</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.919198125245332</v>
+        <v>-8.596092950658383</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.4015404805199076</v>
+        <v>-0.2722984106851278</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.873079790346809</v>
+        <v>-1.751817649080101</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.042647319683887</v>
+        <v>2.115404604443913</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.895244584269374</v>
+        <v>-8.572139409682425</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.3912905579840307</v>
+        <v>-0.2620484881492513</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.849126249370851</v>
+        <v>-1.727864108104143</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.057687950414956</v>
+        <v>2.130445235174981</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.631184645946577</v>
+        <v>-8.308079471359628</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.2989268988166645</v>
+        <v>-0.1696848289818846</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.585066311048055</v>
+        <v>-1.463804169781347</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.202863597246881</v>
+        <v>2.275620882006906</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.924105022441739</v>
+        <v>-7.60099984785479</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.01888208307503003</v>
+        <v>0.1103599867597498</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.585066311048055</v>
+        <v>-1.463804169781347</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.20007656358658</v>
+        <v>2.272833848346605</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.883920724075549</v>
+        <v>-7.560815549488599</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.002464739840712493</v>
+        <v>0.1267773299940673</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.544882012681864</v>
+        <v>-1.423619871415156</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.224530766494136</v>
+        <v>2.297288051254161</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.720520853136186</v>
+        <v>-7.397415678549237</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.06226202975578943</v>
+        <v>0.1915040995905692</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.381482141742502</v>
+        <v>-1.260220000475794</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.321937510278511</v>
+        <v>2.394694795038536</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.487039630906588</v>
+        <v>-7.163934456319638</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.1635789474854814</v>
+        <v>0.2928210173202612</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.148000919512903</v>
+        <v>-1.026738778246195</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.469950672454122</v>
+        <v>2.542707957214147</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.337373239899073</v>
+        <v>-7.014268065312123</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.2205532935755281</v>
+        <v>0.3497953634103079</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.055097428270367</v>
+        <v>-0.933835287003659</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.522800556886684</v>
+        <v>2.59555784164671</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.205097766268186</v>
+        <v>-6.881992591681237</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2688309697749101</v>
+        <v>0.3980730396096894</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.9228219546394807</v>
+        <v>-0.8015598133727724</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.597533327812243</v>
+        <v>2.670290612572269</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.049359433708444</v>
+        <v>-6.726254259121495</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3339413634864434</v>
+        <v>0.4631834333212232</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.7670836220797391</v>
+        <v>-0.6458214808130308</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.693791388035725</v>
+        <v>2.76654867279575</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.800359635024863</v>
+        <v>-6.477254460437914</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4464476241835347</v>
+        <v>0.575689694018314</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.7670836220797391</v>
+        <v>-0.6458214808130308</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.706697729259384</v>
+        <v>2.779455014019409</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.905949624797968</v>
+        <v>-6.582844450211018</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.276235698675074</v>
+        <v>0.4054777685098538</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.8726736118528435</v>
+        <v>-0.7514114705861352</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.515367805796302</v>
+        <v>2.588125090556328</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.924684526916565</v>
+        <v>-6.601579352329615</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3172860797047217</v>
+        <v>0.4465281495395015</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.8782696215129748</v>
+        <v>-0.7570074802462665</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.56055454187731</v>
+        <v>2.633311826637335</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.776744485508965</v>
+        <v>-6.453639310922016</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2565831735795938</v>
+        <v>0.3858252434143736</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.8579487056044173</v>
+        <v>-0.736686564337709</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.452868168734277</v>
+        <v>2.525625453494302</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.723774963254977</v>
+        <v>-6.400669788668027</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.269056996227711</v>
+        <v>0.3982990660624908</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.8049791833504284</v>
+        <v>-0.6837170420837201</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.475935895833192</v>
+        <v>2.548693180593217</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.680226556484286</v>
+        <v>-6.357121381897337</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.279515746840894</v>
+        <v>0.4087578166756738</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.8049791833504284</v>
+        <v>-0.6837170420837201</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.468975283738099</v>
+        <v>2.541732568498124</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.438078163030428</v>
+        <v>-6.114972988443479</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3908374586035803</v>
+        <v>0.5200795284383601</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.8049791833504284</v>
+        <v>-0.6837170420837201</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.483437638119242</v>
+        <v>2.556194922879267</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.329819025907907</v>
+        <v>-6.006713851320957</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.428673233911784</v>
+        <v>0.5579153037465638</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.8049791833504284</v>
+        <v>-0.6837170420837201</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.477969758578437</v>
+        <v>2.550727043338462</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.206527891090776</v>
+        <v>-5.883422716503826</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4754877818492131</v>
+        <v>0.604729851683993</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.6816880485332979</v>
+        <v>-0.5604259072665896</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.549442533479292</v>
+        <v>2.622199818239317</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.185378692187332</v>
+        <v>-5.862273517600383</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4916484396479159</v>
+        <v>0.6208905094826958</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.6605388496298545</v>
+        <v>-0.5392767083631462</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.569833031058684</v>
+        <v>2.642590315818709</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.941613250203888</v>
+        <v>-5.618508075616939</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5849353247883444</v>
+        <v>0.7141773946231238</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.6605388496298545</v>
+        <v>-0.5392767083631462</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.565613739405734</v>
+        <v>2.638371024165759</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.839850429926593</v>
+        <v>-5.516745255339644</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6277647668192783</v>
+        <v>0.7570068366540581</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.6473197812374258</v>
+        <v>-0.5260576399707175</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.575669494361208</v>
+        <v>2.648426779121233</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.590000035977519</v>
+        <v>-5.266894861390569</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7204469993826104</v>
+        <v>0.8496890692173897</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.6473197812374258</v>
+        <v>-0.5260576399707175</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.56841156934491</v>
+        <v>2.641168854104935</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.414107943510086</v>
+        <v>-5.091002768923136</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.794402959890232</v>
+        <v>0.9236450297250118</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.6473197812374258</v>
+        <v>-0.5260576399707175</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.572010692865558</v>
+        <v>2.644767977625583</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.242661480487622</v>
+        <v>-4.919556305900673</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.876309051153771</v>
+        <v>1.005551120988551</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.4758733182149627</v>
+        <v>-0.3546111769482544</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.68820607673359</v>
+        <v>2.760963361493615</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.168371914749283</v>
+        <v>-4.845266740162334</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9050453550654036</v>
+        <v>1.034287424900183</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.4015837524766234</v>
+        <v>-0.2803216112099151</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.731800293792891</v>
+        <v>2.804557578552915</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.104736172515349</v>
+        <v>-4.781630997928399</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.935194453013295</v>
+        <v>1.064436522848075</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.3379480102426889</v>
+        <v>-0.2166858689759806</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.774676540187568</v>
+        <v>2.847433824947593</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.993309413189428</v>
+        <v>-4.670204238602479</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9609594155274586</v>
+        <v>1.090201485362238</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.3379480102426889</v>
+        <v>-0.2166858689759806</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.755870798971364</v>
+        <v>2.828628083731389</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.752878916384568</v>
+        <v>-4.429773741797619</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.05887469087428</v>
+        <v>1.18811676070906</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.09751751343782861</v>
+        <v>0.02374462782887971</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.901872173679158</v>
+        <v>2.974629458439183</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.680636348213373</v>
+        <v>-4.357531173626424</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.091701031977578</v>
+        <v>1.220943101812358</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.09751751343782861</v>
+        <v>0.02374462782887971</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.905801487513978</v>
+        <v>2.978558772274003</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.627638025931986</v>
+        <v>-4.304532851345036</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.113578944807473</v>
+        <v>1.242821014642253</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.04218125443588977</v>
+        <v>0.07908088683081854</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.939681826832481</v>
+        <v>3.012439111592506</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.518833140452259</v>
+        <v>-4.195727965865309</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.154098970219358</v>
+        <v>1.283341040054137</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.04218125443588977</v>
+        <v>0.07908088683081854</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.936679898052475</v>
+        <v>3.0094371828125</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.298812342415248</v>
+        <v>-3.975707167828298</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.243686326444776</v>
+        <v>1.372928396279556</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.09903859063209047</v>
+        <v>0.2203007318987988</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.022990842103877</v>
+        <v>3.095748126863902</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.16594465335197</v>
+        <v>-3.84283947876502</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.31272758487191</v>
+        <v>1.44196965470669</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.09903859063209047</v>
+        <v>0.2203007318987988</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.0388850249057</v>
+        <v>3.111642309665725</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.045771569987472</v>
+        <v>-3.722666395400521</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.361942662658012</v>
+        <v>1.491184732492792</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.2192116739965894</v>
+        <v>0.3404738152632977</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.112134719364701</v>
+        <v>3.184892004124726</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.901099424887734</v>
+        <v>-3.577994250300784</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.429899623259347</v>
+        <v>1.559141693094127</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.3638838190963268</v>
+        <v>0.4851459603630351</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.209026108985984</v>
+        <v>3.281783393746009</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.960974252245427</v>
+        <v>-3.637869077658476</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.391987183717695</v>
+        <v>1.521229253552475</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.3040089917386347</v>
+        <v>0.425271133005343</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.159138703972794</v>
+        <v>3.231895988732819</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.841154021334589</v>
+        <v>-3.518048846747639</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.455204445316239</v>
+        <v>1.584446515151019</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.3040089917386347</v>
+        <v>0.425271133005343</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.174427873207003</v>
+        <v>3.247185157967028</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.843623727796395</v>
+        <v>-3.520518553209445</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.361860762053958</v>
+        <v>1.491102831888738</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.3015392852768286</v>
+        <v>0.4228014265435369</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.080590248652361</v>
+        <v>3.153347533412386</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.911993914120405</v>
+        <v>-3.588888739533455</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.253774549009655</v>
+        <v>1.383016618844436</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.4320771255797518</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.005417529559391</v>
+        <v>3.078174814319416</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.925781966967452</v>
+        <v>-3.602676792380501</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.238696036502728</v>
+        <v>1.367938106337508</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.4320771255797518</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.995854238191282</v>
+        <v>3.068611522951307</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.956775126296157</v>
+        <v>-3.633669951709207</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.051008337811633</v>
+        <v>1.180250407646413</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.4320771255797518</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.820563803231669</v>
+        <v>2.893321087991694</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.781300866503688</v>
+        <v>-3.458195691916738</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.125765273720408</v>
+        <v>1.255007343555188</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.4320771255797518</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.825131035223457</v>
+        <v>2.897888319983482</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.892237119144936</v>
+        <v>-3.569131944557986</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.057132801425116</v>
+        <v>1.186374871259896</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.3108149843130435</v>
+        <v>0.4320771255797518</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.800873063984664</v>
+        <v>2.873630348744689</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.858573573672655</v>
+        <v>-3.535468399085704</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.073729604833934</v>
+        <v>1.202971674668714</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3444785297853253</v>
+        <v>0.4657406710520337</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.824202576487939</v>
+        <v>2.896959861247964</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.798720954468931</v>
+        <v>-3.475615779881981</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.107843038947556</v>
+        <v>1.237085108782336</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3444785297853253</v>
+        <v>0.4657406710520337</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.834374962920071</v>
+        <v>2.907132247680096</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.712477491442554</v>
+        <v>-3.389372316855604</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.137286694731967</v>
+        <v>1.266528764566747</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3444785297853253</v>
+        <v>0.4657406710520337</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.829321233493931</v>
+        <v>2.902078518253957</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.757784310841534</v>
+        <v>-3.434679136254584</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.110939742416901</v>
+        <v>1.240181812251681</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.3036683667760945</v>
+        <v>0.4249305080428029</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.796610911132919</v>
+        <v>2.869368195892943</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.786817415543835</v>
+        <v>-3.463712240956885</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.099878373569082</v>
+        <v>1.229120443403862</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.3036683667760945</v>
+        <v>0.4249305080428029</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.79716278416602</v>
+        <v>2.869920068926045</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.694006934092976</v>
+        <v>-3.370901759506026</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.066275258040791</v>
+        <v>1.195517327875571</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.3964788482269539</v>
+        <v>0.5177409894936622</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.782121764927902</v>
+        <v>2.854879049687926</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.738396403422404</v>
+        <v>-3.415291228835454</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.050392946233621</v>
+        <v>1.179635016068401</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.3520893788975262</v>
+        <v>0.4733515201642345</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.757361559254845</v>
+        <v>2.830118844014871</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.625725185186154</v>
+        <v>-3.302620010599203</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.090537142039844</v>
+        <v>1.219779211874624</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4647605971337764</v>
+        <v>0.5860227384004848</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.820039998708319</v>
+        <v>2.892797283468344</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.513348184003481</v>
+        <v>-3.190243009416531</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.14097923834358</v>
+        <v>1.27022130817836</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4647605971337764</v>
+        <v>0.5860227384004848</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.825531294538986</v>
+        <v>2.898288579299011</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.541128581904834</v>
+        <v>-3.218023407317884</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.141364280951578</v>
+        <v>1.270606350786358</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4369801992324234</v>
+        <v>0.5582423404991317</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.820360257566713</v>
+        <v>2.893117542326738</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.624129862930113</v>
+        <v>-3.301024688343163</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9465194885421195</v>
+        <v>1.0757615583769</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4184093147052496</v>
+        <v>0.539671455971958</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.647573446851062</v>
+        <v>2.720330731611087</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.732743941373444</v>
+        <v>-3.409638766786494</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.023223517883993</v>
+        <v>1.152465587718773</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4184093147052496</v>
+        <v>0.539671455971958</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.767723107570268</v>
+        <v>2.840480392330293</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.697334903125301</v>
+        <v>-3.374229728538351</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.051900159285573</v>
+        <v>1.181142229120353</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4184093147052496</v>
+        <v>0.539671455971958</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.782236133672591</v>
+        <v>2.854993418432616</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.65895124056715</v>
+        <v>-3.3358460659802</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.064673065651202</v>
+        <v>1.193915135485982</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4567929772634008</v>
+        <v>0.5780551185301092</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.80268577254985</v>
+        <v>2.875443057309875</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.481834910531984</v>
+        <v>-3.158729735945034</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.132248626510571</v>
+        <v>1.261490696345351</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4567929772634008</v>
+        <v>0.5780551185301092</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.799414801395153</v>
+        <v>2.872172086155178</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.52692715536553</v>
+        <v>-3.20382198077858</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.114895120339066</v>
+        <v>1.244137190173846</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.394896934094011</v>
+        <v>0.5161590753607194</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.762960567255432</v>
+        <v>2.835717852015457</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.347551734126762</v>
+        <v>-3.024446559539812</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.180432264140987</v>
+        <v>1.309674333975767</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5516736922647296</v>
+        <v>0.672935833531438</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.850813597464277</v>
+        <v>2.923570882224302</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.392565947647368</v>
+        <v>-3.069460773060418</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.143234034064334</v>
+        <v>1.272476103899114</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.521324796950125</v>
+        <v>0.6425869382168334</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.813411715607104</v>
+        <v>2.886169000367129</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.659570457919804</v>
+        <v>-3.336465283332854</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.042123792294306</v>
+        <v>1.171365862129086</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3269617589071764</v>
+        <v>0.4482239001738849</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.702485455120281</v>
+        <v>2.775242739880306</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.760768239356977</v>
+        <v>-3.437663064770026</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.000848601615938</v>
+        <v>1.130090671450718</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2585529453618572</v>
+        <v>0.3798150866285657</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.660644088889591</v>
+        <v>2.733401373649616</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.754257272742664</v>
+        <v>-3.431152098155714</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.00105294981598</v>
+        <v>1.13029501965076</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2585529453618572</v>
+        <v>0.3798150866285657</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.658244050443908</v>
+        <v>2.731001335203933</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.735219145035367</v>
+        <v>-3.412113970448416</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.005192920107144</v>
+        <v>1.134434989941924</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2003693340306627</v>
+        <v>0.3216314752973711</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.619858602853436</v>
+        <v>2.692615887613461</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.766345776185985</v>
+        <v>-3.443240601599034</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.170324136585577</v>
+        <v>1.299566206420357</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2003693340306627</v>
+        <v>0.3216314752973711</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.797440471792116</v>
+        <v>2.870197756552141</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.780212537519902</v>
+        <v>-3.457107362932952</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.165610761038144</v>
+        <v>1.294852830872924</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1625114172968398</v>
+        <v>0.2837735585635482</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.775559050737956</v>
+        <v>2.848316335497981</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.735408365979972</v>
+        <v>-3.412303191393022</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.189540960051042</v>
+        <v>1.318783029885822</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1625114172968398</v>
+        <v>0.2837735585635482</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.781567581134882</v>
+        <v>2.854324865894907</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.58766539574497</v>
+        <v>-3.26456022115802</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.146588369422242</v>
+        <v>1.275830439257022</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3303187745317229</v>
+        <v>0.4515809157984313</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.780202216753011</v>
+        <v>2.852959501513036</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.689680078276191</v>
+        <v>-3.366574903689241</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.108576117941235</v>
+        <v>1.237818187776015</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3303187745317229</v>
+        <v>0.4515809157984313</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.782995838284492</v>
+        <v>2.855753123044517</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.683527372223407</v>
+        <v>-3.360422197636456</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.111699548754007</v>
+        <v>1.240941618588787</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3364714805845072</v>
+        <v>0.4577336218512156</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.787349810307821</v>
+        <v>2.860107095067846</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.700336670373908</v>
+        <v>-3.377231495786958</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.104056306233916</v>
+        <v>1.233298376068697</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3196621824340056</v>
+        <v>0.440924323700714</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.776344708157631</v>
+        <v>2.849101992917656</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.638038671597786</v>
+        <v>-3.314933497010836</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.195311059541186</v>
+        <v>1.324553129375966</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3196621824340056</v>
+        <v>0.440924323700714</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.842680261954452</v>
+        <v>2.915437546714477</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.436248473932628</v>
+        <v>-3.113143299345678</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.078319140321376</v>
+        <v>1.207561210156156</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.51768037460316</v>
+        <v>0.6389425158698684</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.763783178970071</v>
+        <v>2.836540463730096</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.362870376843892</v>
+        <v>-3.039765202256941</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.177960611479046</v>
+        <v>1.307202681313826</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5910584716918965</v>
+        <v>0.7123206129586049</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.878100269545488</v>
+        <v>2.950857554305514</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.460610921468866</v>
+        <v>-3.137505746881916</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.1534921297451</v>
+        <v>1.28273419957988</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5751691935589163</v>
+        <v>0.6964313348256248</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.883194438781744</v>
+        <v>2.955951723541769</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.636948681591795</v>
+        <v>-3.313843507004845</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.0814930065206</v>
+        <v>1.21073507635538</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3988314334359869</v>
+        <v>0.5200935747026953</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.775927763532658</v>
+        <v>2.848685048292683</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.560526635159869</v>
+        <v>-3.237421460572918</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.110553443133299</v>
+        <v>1.239795512968079</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3988314334359869</v>
+        <v>0.5200935747026953</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.774419381572586</v>
+        <v>2.847176666332611</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.5161535035213</v>
+        <v>-3.19304832893435</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.128165563224163</v>
+        <v>1.257407633058943</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4432045650745555</v>
+        <v>0.5644667063412639</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.800906127991164</v>
+        <v>2.873663412751189</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.393319282634133</v>
+        <v>-3.070214108047182</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.17169304571762</v>
+        <v>1.3009351155524</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4432045650745555</v>
+        <v>0.5644667063412639</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.795299922129754</v>
+        <v>2.868057206889779</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.345663552073077</v>
+        <v>-3.022558377486127</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.197137094969847</v>
+        <v>1.326379164804627</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4908602956356112</v>
+        <v>0.6121224369023196</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.830275117494192</v>
+        <v>2.903032402254217</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.245145393574322</v>
+        <v>-2.922040218987372</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.242236731744074</v>
+        <v>1.371478801578854</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5913784541343657</v>
+        <v>0.7126405954010742</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.89547838596817</v>
+        <v>2.968235670728195</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.305811983976711</v>
+        <v>-2.982706809389761</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.204724768058991</v>
+        <v>1.333966837893771</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5096801374158321</v>
+        <v>0.6309422786825405</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.833214068412922</v>
+        <v>2.905971353172947</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.260973582368313</v>
+        <v>-2.937868407781363</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.226757831312978</v>
+        <v>1.355999901147758</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5142235703607015</v>
+        <v>0.63548571162741</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.840037830790472</v>
+        <v>2.912795115550497</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.361732218125312</v>
+        <v>-3.038627043538362</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.190615316641257</v>
+        <v>1.319857386476037</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4253980016336961</v>
+        <v>0.5466601429004045</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.790903429185347</v>
+        <v>2.863660713945372</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.317529381039412</v>
+        <v>-2.994424206452461</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.214176054003454</v>
+        <v>1.343418123838234</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4696008387195966</v>
+        <v>0.590862979986305</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.823304733964724</v>
+        <v>2.896062018724749</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.354508408702855</v>
+        <v>-3.031403234115905</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.197794443407324</v>
+        <v>1.327036513242104</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5065747405109271</v>
+        <v>0.6278368817776355</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.84389907550877</v>
+        <v>2.916656360268795</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.196216991163582</v>
+        <v>-2.873111816576632</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.312358775606073</v>
+        <v>1.441600845440853</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5065747405109271</v>
+        <v>0.6278368817776355</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.89514684069181</v>
+        <v>2.967904125451835</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.988574987529106</v>
+        <v>-2.665469812942156</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.393856281654117</v>
+        <v>1.523098351488897</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7142167441454033</v>
+        <v>0.8354788854121117</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.018172747466749</v>
+        <v>3.090930032226773</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.937542894806578</v>
+        <v>-2.614437720219628</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.409217346981398</v>
+        <v>1.538459416816178</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7652488368679312</v>
+        <v>0.8865109781346396</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.043740231338536</v>
+        <v>3.116497516098561</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.872318713679372</v>
+        <v>-2.549213539092422</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.452494423524985</v>
+        <v>1.581736493359765</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8304730179951368</v>
+        <v>0.9517351592618453</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.100062144107564</v>
+        <v>3.172819428867589</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.834891693608239</v>
+        <v>-2.511786519021288</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.463426203852719</v>
+        <v>1.592668273687499</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8357245560243185</v>
+        <v>0.9569866972910269</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.099174039224353</v>
+        <v>3.171931323984378</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.855003349642947</v>
+        <v>-2.531898175055997</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.456638333770076</v>
+        <v>1.585880403604856</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8467519010217377</v>
+        <v>0.9680140422884461</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.107047238554045</v>
+        <v>3.17980452331407</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.801258535215742</v>
+        <v>-2.478153360628792</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.638694030562169</v>
+        <v>1.767936100396949</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.8568152104621997</v>
+        <v>0.9780773517289081</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.273642995239533</v>
+        <v>3.346400279999558</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.7774669666096</v>
+        <v>-2.45436179202265</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.768323567222443</v>
+        <v>1.897565637057223</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.8806067790683419</v>
+        <v>1.00186892033505</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.408030845621036</v>
+        <v>3.480788130381061</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.751382882345792</v>
+        <v>-2.428277707758842</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.770465176941825</v>
+        <v>1.899707246776605</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.8806067790683419</v>
+        <v>1.00186892033505</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.399738821634894</v>
+        <v>3.47249610639492</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.673251701496845</v>
+        <v>-2.350146526909895</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.799910844865183</v>
+        <v>1.929152914699963</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9547835899520265</v>
+        <v>1.076045731218735</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.442438103748885</v>
+        <v>3.51519538850891</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.664359240103562</v>
+        <v>-2.341254065516612</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.821022235149288</v>
+        <v>1.950264304984068</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9547835899520265</v>
+        <v>1.076045731218735</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.459992509475676</v>
+        <v>3.532749794235701</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.83283535707344</v>
+        <v>-2.50973018248649</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.745486835765921</v>
+        <v>1.874728905600701</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9268357542354457</v>
+        <v>1.048097895502154</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.435078855450311</v>
+        <v>3.507836140210337</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.135035828211857</v>
+        <v>-1.811930653624906</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.005876344498416</v>
+        <v>2.135118414333196</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8564876948650351</v>
+        <v>0.9777498361317436</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.374139717015927</v>
+        <v>3.446897001775952</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.112314724528704</v>
+        <v>-1.789209549941754</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.005628808468581</v>
+        <v>2.134870878303361</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8564876948650351</v>
+        <v>0.9777498361317436</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.364803739512832</v>
+        <v>3.437561024272857</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.11058968123866</v>
+        <v>-1.78748450665171</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.165224951635768</v>
+        <v>2.294467021470548</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.8582127381550788</v>
+        <v>0.9794748794217873</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.524744891338027</v>
+        <v>3.597502176098052</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.265370688016915</v>
+        <v>-1.942265513429966</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.140390371418112</v>
+        <v>2.269632441252893</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8248450641006027</v>
+        <v>0.9461072053673112</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.541802109398988</v>
+        <v>3.614559394159013</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.213935354632256</v>
+        <v>-1.890830180045306</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.157639860761521</v>
+        <v>2.286881930596302</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8762803974852623</v>
+        <v>0.9975425387519707</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.569338665419329</v>
+        <v>3.642095950179354</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.186984130305768</v>
+        <v>-1.863878955718818</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.178426504136858</v>
+        <v>2.307668573971638</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8911607435129815</v>
+        <v>1.01242288477969</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.588273026680702</v>
+        <v>3.661030311440727</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.322937138362084</v>
+        <v>-1.999831963775134</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.308148433059292</v>
+        <v>2.437390502894071</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8911607435129815</v>
+        <v>1.01242288477969</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.772376158825661</v>
+        <v>3.845133443585687</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.345345256166956</v>
+        <v>-2.022240081580006</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.291301880840336</v>
+        <v>2.420543950675116</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8911607435129815</v>
+        <v>1.01242288477969</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.764492853728655</v>
+        <v>3.83725013848868</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.493351023646356</v>
+        <v>-2.170245849059405</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.234153573398213</v>
+        <v>2.363395643232993</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.80443373464944</v>
+        <v>0.9256958759161484</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.714510647960167</v>
+        <v>3.787267932720192</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.502791949534886</v>
+        <v>-2.179686774947935</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.286630920764648</v>
+        <v>2.415872990599429</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.9268608521928314</v>
+        <v>1.04812299345954</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.844220636208049</v>
+        <v>3.916977920968074</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.501505185995329</v>
+        <v>-2.178400011408379</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.290036720725772</v>
+        <v>2.419278790560552</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.928147615732388</v>
+        <v>1.049409756999096</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.847883788877084</v>
+        <v>3.920641073637109</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.503062239984621</v>
+        <v>-2.17995706539767</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.287525712023831</v>
+        <v>2.416767781858611</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.928147615732388</v>
+        <v>1.049409756999096</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.845995601770859</v>
+        <v>3.918752886530884</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.510334125508085</v>
+        <v>-2.187228950921135</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.279437187417307</v>
+        <v>2.408679257252087</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9208757302089232</v>
+        <v>1.042137871475632</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.836452700059643</v>
+        <v>3.909209984819667</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.508493106449834</v>
+        <v>-2.185387931862884</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.27860760525076</v>
+        <v>2.40784967508554</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9221439568803916</v>
+        <v>1.0434060981471</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.835647646272676</v>
+        <v>3.908404931032701</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.515401811949515</v>
+        <v>-2.192296637362564</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.288917529916806</v>
+        <v>2.418159599751586</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9221439568803916</v>
+        <v>1.0434060981471</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.848721053138594</v>
+        <v>3.92147833789862</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.516963454764374</v>
+        <v>-2.193858280177424</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.288292872790862</v>
+        <v>2.417534942625642</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9221439568803916</v>
+        <v>1.0434060981471</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.848721053138594</v>
+        <v>3.92147833789862</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.544864241873847</v>
+        <v>-2.221759067286897</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.275656599074075</v>
+        <v>2.404898668908855</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.8875470327374568</v>
+        <v>1.008809174004165</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.826486939779835</v>
+        <v>3.89924422453986</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.547897239386521</v>
+        <v>-2.224792064799571</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.271207844046204</v>
+        <v>2.400449913880984</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8845140352247829</v>
+        <v>1.005776176491491</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.82143158524943</v>
+        <v>3.894188870009455</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.567958560663028</v>
+        <v>-2.244853386076078</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.329889275126106</v>
+        <v>2.459131344960885</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.8644527139482758</v>
+        <v>0.9857148552149841</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.876100752074029</v>
+        <v>3.948858036834054</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.824679378657852</v>
+        <v>-2.501574204070902</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.367512666930023</v>
+        <v>2.496754736764803</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.756038139804461</v>
+        <v>0.8773002810711693</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.951363726589587</v>
+        <v>4.024121011349613</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.978665796433992</v>
+        <v>-2.655560621847042</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.374898368965206</v>
+        <v>2.504140438799986</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.756038139804461</v>
+        <v>0.8773002810711693</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.020343995735227</v>
+        <v>4.093101280495253</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.928143892606327</v>
+        <v>-2.605038718019376</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.381158332616394</v>
+        <v>2.510400402451173</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.756038139804461</v>
+        <v>0.8773002810711693</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.006395197855348</v>
+        <v>4.079152482615373</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.180619046614051</v>
+        <v>-2.857513872027101</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.292038760068718</v>
+        <v>2.421280829903498</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.756038139804461</v>
+        <v>0.8773002810711693</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.018265686910762</v>
+        <v>4.091022971670787</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.450091848535759</v>
+        <v>-3.126986673948809</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.185460173818978</v>
+        <v>2.314702243653758</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.756038139804461</v>
+        <v>0.8773002810711693</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.019476221429706</v>
+        <v>4.092233506189731</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.41656572832805</v>
+        <v>3.851213545447334</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.455089829280599</v>
+        <v>3.774430059950164</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.450091848535759</v>
+        <v>-3.126986673948809</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.185460173818978</v>
+        <v>2.314702243653758</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.756038139804461</v>
+        <v>0.8773002810711693</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.448153626266967</v>
+        <v>3.767493856936531</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240710.xlsx
+++ b/tame_output/ON/bt/strategyON_20240710.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>34.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-70.3%</t>
+          <t>-72.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.5%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.1%</t>
+          <t>123.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-49.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-65.0%</t>
+          <t>-68.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.6%</t>
+          <t>452.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-474.3%</t>
+          <t>-505.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.8%</t>
+          <t>-35.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>481.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-144.8%</t>
+          <t>-157.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.6%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-132.2%</t>
+          <t>-123.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-136.3%</t>
+          <t>-152.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>94.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-69.3%</t>
+          <t>-100.8%</t>
         </is>
       </c>
     </row>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.334486617436109</v>
+        <v>-5.606854586351314</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.982527904640722</v>
+        <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.5596906225558451</v>
+        <v>-0.6809527638225534</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.780864602395406</v>
+        <v>2.708107317635381</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.743075394616787</v>
+        <v>-6.015443363531993</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8178539377832097</v>
+        <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.9682793997365235</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.534472880101758</v>
+        <v>2.461715595341733</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.019651494932619</v>
+        <v>-6.292019463847826</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7024089301283372</v>
+        <v>0.5934617425622548</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.9682793997365235</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.529658312573218</v>
+        <v>2.456901027813193</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.436043369219616</v>
+        <v>-6.708411338134823</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.5338462310224159</v>
+        <v>0.4248990434563331</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.9682793997365235</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.527652363182096</v>
+        <v>2.454895078422071</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.680314769946686</v>
+        <v>-6.952682738861893</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4463963614002671</v>
+        <v>0.3374491738341843</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.9682793997365235</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.537911053850775</v>
+        <v>2.46515376909075</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.885565789183446</v>
+        <v>-7.157933758098653</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.360395518851258</v>
+        <v>0.2514483312851752</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.9682793997365235</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.53401061899647</v>
+        <v>2.461253334236445</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.04914566736783</v>
+        <v>-7.321513636283036</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2933684876325056</v>
+        <v>0.1844213000664228</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.9682793997365235</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.532415539051471</v>
+        <v>2.459658254291446</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.345807009178027</v>
+        <v>-7.618174978093234</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1784829268376349</v>
+        <v>0.0695357392715521</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.037022535470402</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.494948633540352</v>
+        <v>2.422191348780327</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.53252671748733</v>
+        <v>-7.804894686402537</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.09976873897951055</v>
+        <v>-0.009178448586572241</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.037022535470402</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.490922329005949</v>
+        <v>2.418165044245924</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.915528106229961</v>
+        <v>-8.187896075145167</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.05353391783912587</v>
+        <v>-0.1624811054052082</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.037022535470402</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.490820227684365</v>
+        <v>2.41806294292434</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-8.097397897214996</v>
+        <v>-8.369765866130201</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.1237103182617099</v>
+        <v>-0.2326575058277922</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.218892326455437</v>
+        <v>-1.340154467722146</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.384269869064774</v>
+        <v>2.311512584304749</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.456928219718998</v>
+        <v>-8.729296188634203</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2621721439652607</v>
+        <v>-0.3711193315313426</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.218892326455437</v>
+        <v>-1.340154467722146</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.389620172362824</v>
+        <v>2.316862887602799</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.50727728317322</v>
+        <v>-8.779645252088425</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2743957493897717</v>
+        <v>-0.3833429369558536</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.269241389909659</v>
+        <v>-1.390503531176368</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.367326754247468</v>
+        <v>2.294569469487443</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.604896560594616</v>
+        <v>-8.877264529509821</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.3104017097365612</v>
+        <v>-0.4193488973026436</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.366860667331056</v>
+        <v>-1.488122808597764</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.311796938416399</v>
+        <v>2.239039653656374</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.752422648600259</v>
+        <v>-9.024790617515464</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.3665185886172462</v>
+        <v>-0.4754657761833285</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.514386755336699</v>
+        <v>-1.635648896603408</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.226174841934585</v>
+        <v>2.15341755717456</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.956680823930123</v>
+        <v>-9.229048792845328</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.4427086616305496</v>
+        <v>-0.5516558491966315</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.642025699950688</v>
+        <v>-1.763287841217397</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.155104672284834</v>
+        <v>2.082347387524809</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.990333662438596</v>
+        <v>-9.262701631353801</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.4516872425495029</v>
+        <v>-0.5606344301155848</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.742439067867726</v>
+        <v>-1.863701209134434</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.099339206019048</v>
+        <v>2.026581921259023</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.916863830771147</v>
+        <v>-9.189231799686352</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.4069276083891022</v>
+        <v>-0.5158747959551842</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.668969236200277</v>
+        <v>-1.790231377466986</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.158792806512938</v>
+        <v>2.086035521752913</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-9.091988248157691</v>
+        <v>-9.364356217072896</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4624221545962026</v>
+        <v>-0.5713693421622845</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.844093653586821</v>
+        <v>-1.965355794853529</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.068273376828529</v>
+        <v>1.995516092068503</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.32644034217218</v>
+        <v>-9.598808311087385</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5634221571035947</v>
+        <v>-0.6723693446696766</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.844093653586821</v>
+        <v>-1.965355794853529</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.061054211926932</v>
+        <v>1.988296927166908</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.430815073198627</v>
+        <v>-9.703183042113832</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.6118442402881494</v>
+        <v>-0.7207914278542313</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.948468384613267</v>
+        <v>-2.069730525879975</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.991757182537089</v>
+        <v>1.918999897777064</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.483601228798953</v>
+        <v>-9.755969197714158</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.6318429126897236</v>
+        <v>-0.7407901002558055</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.044143871195664</v>
+        <v>-2.165406012462372</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.935467680426207</v>
+        <v>1.862710395666182</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.609638022167243</v>
+        <v>-9.882005991082448</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6795639014079247</v>
+        <v>-0.7885110889740066</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.018892248385922</v>
+        <v>-2.14015438965263</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.953312382741167</v>
+        <v>1.880555097981142</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.552566250271312</v>
+        <v>-9.824934219186517</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6527448569631513</v>
+        <v>-0.7616920445292337</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.018892248385922</v>
+        <v>-2.14015438965263</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.957302718427568</v>
+        <v>1.884545433667543</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.694238091995432</v>
+        <v>-9.966606060910637</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.7108888205515411</v>
+        <v>-0.8198360081176235</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.018892248385922</v>
+        <v>-2.14015438965263</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.955827491528826</v>
+        <v>1.883070206768801</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.644647247570598</v>
+        <v>-9.917015216485803</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6759990726167353</v>
+        <v>-0.7849462601828172</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.969301403961088</v>
+        <v>-2.090563545227796</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.000635408348598</v>
+        <v>1.927878123588574</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.495728913098741</v>
+        <v>-9.768096882013946</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.6294828724746755</v>
+        <v>-0.7384300600407578</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.938051813225915</v>
+        <v>-2.059313954492623</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.006334029143019</v>
+        <v>1.933576744382995</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.269883760379329</v>
+        <v>-9.542251729294534</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.5295657383507022</v>
+        <v>-0.6385129259167841</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.896125137638751</v>
+        <v>-2.017387278905459</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.041069107531526</v>
+        <v>1.968311822771502</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.145305104041737</v>
+        <v>-9.417673072956942</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4785951312596066</v>
+        <v>-0.5875423188256885</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.896125137638751</v>
+        <v>-2.017387278905459</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.042208252087585</v>
+        <v>1.96945096732756</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.198200392086024</v>
+        <v>-9.470568361001229</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4971194723152137</v>
+        <v>-0.6060666598812956</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.891169791550305</v>
+        <v>-2.012431932817013</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.047815233902761</v>
+        <v>1.975057949142736</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.126067216798143</v>
+        <v>-9.398435185713348</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4625324979614245</v>
+        <v>-0.5714796855275068</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.891169791550305</v>
+        <v>-2.012431932817013</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.053548938141397</v>
+        <v>1.980791653381372</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-9.054700824188496</v>
+        <v>-9.327068793103701</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4437232033114311</v>
+        <v>-0.552670390877513</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.819803398940657</v>
+        <v>-1.941065540207365</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.086631511313321</v>
+        <v>2.013874226553296</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.961241790203271</v>
+        <v>-9.233609759118476</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.4162230710302488</v>
+        <v>-0.5251702585963307</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.819803398940657</v>
+        <v>-1.941065540207365</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.076748030000413</v>
+        <v>2.003990745240388</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.693999989334873</v>
+        <v>-8.966367958250078</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3111609111822635</v>
+        <v>-0.4201080987483454</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.819803398940657</v>
+        <v>-1.941065540207365</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.074913469501039</v>
+        <v>2.002156184741015</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.596092950658383</v>
+        <v>-8.868460919573588</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2722984106851278</v>
+        <v>-0.3812455982512097</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.751817649080101</v>
+        <v>-1.873079790346809</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.115404604443913</v>
+        <v>2.042647319683887</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.572139409682425</v>
+        <v>-8.84450737859763</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2620484881492513</v>
+        <v>-0.3709956757153332</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.727864108104143</v>
+        <v>-1.849126249370851</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.130445235174981</v>
+        <v>2.057687950414956</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.308079471359628</v>
+        <v>-8.580447440274833</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1696848289818846</v>
+        <v>-0.2786320165479665</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.463804169781347</v>
+        <v>-1.585066311048055</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.275620882006906</v>
+        <v>2.202863597246881</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.60099984785479</v>
+        <v>-7.873367816769995</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1103599867597498</v>
+        <v>0.00141279919366788</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.463804169781347</v>
+        <v>-1.585066311048055</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.272833848346605</v>
+        <v>2.20007656358658</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.560815549488599</v>
+        <v>-7.833183518403804</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1267773299940673</v>
+        <v>0.01783014242798542</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.423619871415156</v>
+        <v>-1.544882012681864</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.297288051254161</v>
+        <v>2.224530766494136</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.397415678549237</v>
+        <v>-7.669783647464442</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1915040995905692</v>
+        <v>0.08255691202448734</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.260220000475794</v>
+        <v>-1.381482141742502</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.394694795038536</v>
+        <v>2.321937510278511</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.163934456319638</v>
+        <v>-7.436302425234843</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2928210173202612</v>
+        <v>0.1838738297541793</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.026738778246195</v>
+        <v>-1.148000919512903</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.542707957214147</v>
+        <v>2.469950672454122</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.014268065312123</v>
+        <v>-7.286636034227328</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3497953634103079</v>
+        <v>0.240848175844226</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.933835287003659</v>
+        <v>-1.055097428270367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.59555784164671</v>
+        <v>2.522800556886684</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.881992591681237</v>
+        <v>-7.154360560596442</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3980730396096894</v>
+        <v>0.2891258520436075</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.8015598133727724</v>
+        <v>-0.9228219546394807</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.670290612572269</v>
+        <v>2.597533327812243</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.726254259121495</v>
+        <v>-6.9986222280367</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4631834333212232</v>
+        <v>0.3542362457551409</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.6458214808130308</v>
+        <v>-0.7670836220797391</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.76654867279575</v>
+        <v>2.693791388035725</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.477254460437914</v>
+        <v>-6.749622429353119</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.575689694018314</v>
+        <v>0.4667425064522321</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.6458214808130308</v>
+        <v>-0.7670836220797391</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.779455014019409</v>
+        <v>2.706697729259384</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.582844450211018</v>
+        <v>-6.855212419126223</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4054777685098538</v>
+        <v>0.2965305809437719</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.7514114705861352</v>
+        <v>-0.8726736118528435</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.588125090556328</v>
+        <v>2.515367805796302</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.601579352329615</v>
+        <v>-6.87394732124482</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4465281495395015</v>
+        <v>0.3375809619734191</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.7570074802462665</v>
+        <v>-0.8782696215129748</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.633311826637335</v>
+        <v>2.56055454187731</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.453639310922016</v>
+        <v>-6.726007279837221</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3858252434143736</v>
+        <v>0.2768780558482913</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.736686564337709</v>
+        <v>-0.8579487056044173</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.525625453494302</v>
+        <v>2.452868168734277</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.400669788668027</v>
+        <v>-6.673037757583232</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3982990660624908</v>
+        <v>0.2893518784964089</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.6837170420837201</v>
+        <v>-0.8049791833504284</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.548693180593217</v>
+        <v>2.475935895833192</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.357121381897337</v>
+        <v>-6.629489350812542</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4087578166756738</v>
+        <v>0.2998106291095919</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.6837170420837201</v>
+        <v>-0.8049791833504284</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.541732568498124</v>
+        <v>2.468975283738099</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.114972988443479</v>
+        <v>-6.387340957358684</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5200795284383601</v>
+        <v>0.4111323408722782</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.6837170420837201</v>
+        <v>-0.8049791833504284</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.556194922879267</v>
+        <v>2.483437638119242</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.006713851320957</v>
+        <v>-6.279081820236162</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5579153037465638</v>
+        <v>0.4489681161804819</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.6837170420837201</v>
+        <v>-0.8049791833504284</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.550727043338462</v>
+        <v>2.477969758578437</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.883422716503826</v>
+        <v>-6.155790685419031</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.604729851683993</v>
+        <v>0.4957826641179111</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.5604259072665896</v>
+        <v>-0.6816880485332979</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.622199818239317</v>
+        <v>2.549442533479292</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.862273517600383</v>
+        <v>-6.134641486515588</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6208905094826958</v>
+        <v>0.5119433219166134</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.5392767083631462</v>
+        <v>-0.6605388496298545</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.642590315818709</v>
+        <v>2.569833031058684</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.618508075616939</v>
+        <v>-5.890876044532144</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7141773946231238</v>
+        <v>0.6052302070570419</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.5392767083631462</v>
+        <v>-0.6605388496298545</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.638371024165759</v>
+        <v>2.565613739405734</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.516745255339644</v>
+        <v>-5.789113224254849</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7570068366540581</v>
+        <v>0.6480596490879758</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.5260576399707175</v>
+        <v>-0.6473197812374258</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.648426779121233</v>
+        <v>2.575669494361208</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.266894861390569</v>
+        <v>-5.539262830305774</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8496890692173897</v>
+        <v>0.7407418816513078</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.5260576399707175</v>
+        <v>-0.6473197812374258</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.641168854104935</v>
+        <v>2.56841156934491</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.091002768923136</v>
+        <v>-5.363370737838341</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9236450297250118</v>
+        <v>0.8146978421589299</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.5260576399707175</v>
+        <v>-0.6473197812374258</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.644767977625583</v>
+        <v>2.572010692865558</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.919556305900673</v>
+        <v>-5.191924274815878</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.005551120988551</v>
+        <v>0.8966039334224689</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.3546111769482544</v>
+        <v>-0.4758733182149627</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.760963361493615</v>
+        <v>2.68820607673359</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.845266740162334</v>
+        <v>-5.117634709077539</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.034287424900183</v>
+        <v>0.9253402373341015</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.2803216112099151</v>
+        <v>-0.4015837524766234</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.804557578552915</v>
+        <v>2.731800293792891</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.781630997928399</v>
+        <v>-5.053998966843604</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.064436522848075</v>
+        <v>0.9554893352819924</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.2166858689759806</v>
+        <v>-0.3379480102426889</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.847433824947593</v>
+        <v>2.774676540187568</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.670204238602479</v>
+        <v>-4.942572207517684</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.090201485362238</v>
+        <v>0.9812542977961562</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.2166858689759806</v>
+        <v>-0.3379480102426889</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.828628083731389</v>
+        <v>2.755870798971364</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.429773741797619</v>
+        <v>-4.742767969509496</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.18811676070906</v>
+        <v>1.062919069624309</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.02374462782887971</v>
+        <v>-0.1381437722345013</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.974629458439183</v>
+        <v>2.877496418401154</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.357531173626424</v>
+        <v>-4.670525401338302</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.220943101812358</v>
+        <v>1.095745410727607</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.02374462782887971</v>
+        <v>-0.1381437722345013</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.978558772274003</v>
+        <v>2.881425732235974</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.304532851345036</v>
+        <v>-4.617527079056914</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.242821014642253</v>
+        <v>1.117623323557502</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.07908088683081854</v>
+        <v>-0.08280751323256247</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.012439111592506</v>
+        <v>2.915306071554478</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.195727965865309</v>
+        <v>-4.508722193577187</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.283341040054137</v>
+        <v>1.158143348969386</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.07908088683081854</v>
+        <v>-0.08280751323256247</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.0094371828125</v>
+        <v>2.912304142774471</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.975707167828298</v>
+        <v>-4.288701395540176</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.372928396279556</v>
+        <v>1.247730705194805</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2203007318987988</v>
+        <v>0.05841233183541777</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.095748126863902</v>
+        <v>2.998615086825873</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.84283947876502</v>
+        <v>-4.155833706476899</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.44196965470669</v>
+        <v>1.316771963621939</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2203007318987988</v>
+        <v>0.05841233183541777</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.111642309665725</v>
+        <v>3.014509269627696</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.722666395400521</v>
+        <v>-4.0356606231124</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.491184732492792</v>
+        <v>1.36598704140804</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3404738152632977</v>
+        <v>0.1785854151999167</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.184892004124726</v>
+        <v>3.087758964086698</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.577994250300784</v>
+        <v>-3.890988478012662</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.559141693094127</v>
+        <v>1.433944002009375</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.4851459603630351</v>
+        <v>0.3232575602996541</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.281783393746009</v>
+        <v>3.18465035370798</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.637869077658476</v>
+        <v>-3.950863305370355</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.521229253552475</v>
+        <v>1.396031562467724</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.425271133005343</v>
+        <v>0.263382732941962</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.231895988732819</v>
+        <v>3.134762948694791</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.518048846747639</v>
+        <v>-3.831043074459517</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.584446515151019</v>
+        <v>1.459248824066268</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.425271133005343</v>
+        <v>0.263382732941962</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.247185157967028</v>
+        <v>3.150052117929</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.520518553209445</v>
+        <v>-3.833512780921323</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.491102831888738</v>
+        <v>1.365905140803987</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4228014265435369</v>
+        <v>0.2609130264801559</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.153347533412386</v>
+        <v>3.056214493374357</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.588888739533455</v>
+        <v>-3.901882967245333</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.383016618844436</v>
+        <v>1.257818927759684</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4320771255797518</v>
+        <v>0.2701887255163708</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.078174814319416</v>
+        <v>2.981041774281388</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.602676792380501</v>
+        <v>-3.91567102009238</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.367938106337508</v>
+        <v>1.242740415252757</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4320771255797518</v>
+        <v>0.2701887255163708</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.068611522951307</v>
+        <v>2.971478482913279</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.633669951709207</v>
+        <v>-3.946664179421085</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.180250407646413</v>
+        <v>1.055052716561661</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4320771255797518</v>
+        <v>0.2701887255163708</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.893321087991694</v>
+        <v>2.796188047953666</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.458195691916738</v>
+        <v>-3.771189919628616</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.255007343555188</v>
+        <v>1.129809652470437</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4320771255797518</v>
+        <v>0.2701887255163708</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.897888319983482</v>
+        <v>2.800755279945454</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.569131944557986</v>
+        <v>-3.882126172269865</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.186374871259896</v>
+        <v>1.061177180175145</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4320771255797518</v>
+        <v>0.2701887255163708</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.873630348744689</v>
+        <v>2.776497308706661</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.535468399085704</v>
+        <v>-3.848462626797583</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.202971674668714</v>
+        <v>1.077773983583963</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4657406710520337</v>
+        <v>0.3038522709886526</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.896959861247964</v>
+        <v>2.799826821209935</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.475615779881981</v>
+        <v>-3.78861000759386</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.237085108782336</v>
+        <v>1.111887417697585</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4657406710520337</v>
+        <v>0.3038522709886526</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.907132247680096</v>
+        <v>2.809999207642067</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.389372316855604</v>
+        <v>-3.702366544567482</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.266528764566747</v>
+        <v>1.141331073481996</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4657406710520337</v>
+        <v>0.3038522709886526</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.902078518253957</v>
+        <v>2.804945478215928</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.434679136254584</v>
+        <v>-3.747673363966462</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.240181812251681</v>
+        <v>1.114984121166929</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4249305080428029</v>
+        <v>0.2630421079794218</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.869368195892943</v>
+        <v>2.772235155854915</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.463712240956885</v>
+        <v>-3.776706468668764</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.229120443403862</v>
+        <v>1.10392275231911</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4249305080428029</v>
+        <v>0.2630421079794218</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.869920068926045</v>
+        <v>2.772787028888017</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.370901759506026</v>
+        <v>-3.683895987217904</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.195517327875571</v>
+        <v>1.07031963679082</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5177409894936622</v>
+        <v>0.3558525894302812</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.854879049687926</v>
+        <v>2.757746009649898</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.415291228835454</v>
+        <v>-3.728285456547332</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.179635016068401</v>
+        <v>1.054437324983649</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4733515201642345</v>
+        <v>0.3114631201008535</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.830118844014871</v>
+        <v>2.732985803976842</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.302620010599203</v>
+        <v>-3.615614238311082</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.219779211874624</v>
+        <v>1.094581520789873</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5860227384004848</v>
+        <v>0.4241343383371037</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.892797283468344</v>
+        <v>2.795664243430315</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.190243009416531</v>
+        <v>-3.503237237128409</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.27022130817836</v>
+        <v>1.145023617093609</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5860227384004848</v>
+        <v>0.4241343383371037</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.898288579299011</v>
+        <v>2.801155539260982</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.218023407317884</v>
+        <v>-3.531017635029762</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.270606350786358</v>
+        <v>1.145408659701607</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5582423404991317</v>
+        <v>0.3963539404357507</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.893117542326738</v>
+        <v>2.79598450228871</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.301024688343163</v>
+        <v>-3.614018916055041</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.0757615583769</v>
+        <v>0.9505638672921484</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.539671455971958</v>
+        <v>0.3777830559085769</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.720330731611087</v>
+        <v>2.623197691573059</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.409638766786494</v>
+        <v>-3.722632994498372</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.152465587718773</v>
+        <v>1.027267896634021</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.539671455971958</v>
+        <v>0.3777830559085769</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.840480392330293</v>
+        <v>2.743347352292264</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.374229728538351</v>
+        <v>-3.68722395625023</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.181142229120353</v>
+        <v>1.055944538035602</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.539671455971958</v>
+        <v>0.3777830559085769</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.854993418432616</v>
+        <v>2.757860378394587</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.3358460659802</v>
+        <v>-3.648840293692079</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.193915135485982</v>
+        <v>1.068717444401231</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5780551185301092</v>
+        <v>0.4161667184667281</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.875443057309875</v>
+        <v>2.778310017271846</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.158729735945034</v>
+        <v>-3.471723963656912</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.261490696345351</v>
+        <v>1.1362930052606</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5780551185301092</v>
+        <v>0.4161667184667281</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.872172086155178</v>
+        <v>2.775039046117149</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.20382198077858</v>
+        <v>-3.516816208490458</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.244137190173846</v>
+        <v>1.118939499089094</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5161590753607194</v>
+        <v>0.3542706752973383</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.835717852015457</v>
+        <v>2.738584811977428</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.024446559539812</v>
+        <v>-3.33744078725169</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.309674333975767</v>
+        <v>1.184476642891016</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.672935833531438</v>
+        <v>0.511047433468057</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.923570882224302</v>
+        <v>2.826437842186274</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.069460773060418</v>
+        <v>-3.382455000772297</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.272476103899114</v>
+        <v>1.147278412814363</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6425869382168334</v>
+        <v>0.4806985381534524</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.886169000367129</v>
+        <v>2.789035960329101</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.336465283332854</v>
+        <v>-3.649459511044732</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.171365862129086</v>
+        <v>1.046168171044335</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4482239001738849</v>
+        <v>0.2863355001105038</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.775242739880306</v>
+        <v>2.678109699842278</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.437663064770026</v>
+        <v>-3.750657292481905</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.130090671450718</v>
+        <v>1.004892980365967</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.3798150866285657</v>
+        <v>0.2179266865651847</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.733401373649616</v>
+        <v>2.636268333611587</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.431152098155714</v>
+        <v>-3.744146325867592</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.13029501965076</v>
+        <v>1.005097328566009</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.3798150866285657</v>
+        <v>0.2179266865651847</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.731001335203933</v>
+        <v>2.633868295165904</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.412113970448416</v>
+        <v>-3.725108198160295</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.134434989941924</v>
+        <v>1.009237298857173</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3216314752973711</v>
+        <v>0.1597430752339901</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.692615887613461</v>
+        <v>2.595482847575432</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.443240601599034</v>
+        <v>-3.756234829310913</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.299566206420357</v>
+        <v>1.174368515335606</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3216314752973711</v>
+        <v>0.1597430752339901</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.870197756552141</v>
+        <v>2.773064716514113</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.457107362932952</v>
+        <v>-3.77010159064483</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.294852830872924</v>
+        <v>1.169655139788172</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.2837735585635482</v>
+        <v>0.1218851585001672</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.848316335497981</v>
+        <v>2.751183295459953</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.412303191393022</v>
+        <v>-3.7252974191049</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.318783029885822</v>
+        <v>1.19358533880107</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.2837735585635482</v>
+        <v>0.1218851585001672</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.854324865894907</v>
+        <v>2.757191825856879</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.26456022115802</v>
+        <v>-3.577554448869898</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.275830439257022</v>
+        <v>1.150632748172271</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4515809157984313</v>
+        <v>0.2896925157350503</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.852959501513036</v>
+        <v>2.755826461475008</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.366574903689241</v>
+        <v>-3.679569131401119</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.237818187776015</v>
+        <v>1.112620496691263</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4515809157984313</v>
+        <v>0.2896925157350503</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.855753123044517</v>
+        <v>2.758620083006489</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.360422197636456</v>
+        <v>-3.673416425348335</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.240941618588787</v>
+        <v>1.115743927504036</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4577336218512156</v>
+        <v>0.2958452217878346</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.860107095067846</v>
+        <v>2.762974055029818</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.377231495786958</v>
+        <v>-3.690225723498836</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.233298376068697</v>
+        <v>1.108100684983945</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.440924323700714</v>
+        <v>0.279035923637333</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.849101992917656</v>
+        <v>2.751968952879627</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.314933497010836</v>
+        <v>-3.627927724722714</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.324553129375966</v>
+        <v>1.199355438291215</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.440924323700714</v>
+        <v>0.279035923637333</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.915437546714477</v>
+        <v>2.818304506676448</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.113143299345678</v>
+        <v>-3.426137527057556</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.207561210156156</v>
+        <v>1.082363519071405</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6389425158698684</v>
+        <v>0.4770541158064874</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.836540463730096</v>
+        <v>2.739407423692068</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.039765202256941</v>
+        <v>-3.35275942996882</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.307202681313826</v>
+        <v>1.182004990229075</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.7123206129586049</v>
+        <v>0.5504322128952239</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.950857554305514</v>
+        <v>2.853724514267485</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.137505746881916</v>
+        <v>-3.450499974593794</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.28273419957988</v>
+        <v>1.157536508495129</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6964313348256248</v>
+        <v>0.5345429347622437</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.955951723541769</v>
+        <v>2.85881868350374</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.313843507004845</v>
+        <v>-3.626837734716724</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.21073507635538</v>
+        <v>1.085537385270629</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5200935747026953</v>
+        <v>0.3582051746393143</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.848685048292683</v>
+        <v>2.751552008254654</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.237421460572918</v>
+        <v>-3.550415688284797</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.239795512968079</v>
+        <v>1.114597821883328</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5200935747026953</v>
+        <v>0.3582051746393143</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.847176666332611</v>
+        <v>2.750043626294583</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.19304832893435</v>
+        <v>-3.506042556646228</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.257407633058943</v>
+        <v>1.132209941974192</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5644667063412639</v>
+        <v>0.4025783062778829</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.873663412751189</v>
+        <v>2.77653037271316</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.070214108047182</v>
+        <v>-3.383208335759061</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.3009351155524</v>
+        <v>1.175737424467649</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5644667063412639</v>
+        <v>0.4025783062778829</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.868057206889779</v>
+        <v>2.770924166851751</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.022558377486127</v>
+        <v>-3.335552605198005</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.326379164804627</v>
+        <v>1.201181473719876</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6121224369023196</v>
+        <v>0.4502340368389385</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.903032402254217</v>
+        <v>2.805899362216189</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.922040218987372</v>
+        <v>-3.235034446699251</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.371478801578854</v>
+        <v>1.246281110494103</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7126405954010742</v>
+        <v>0.550752195337693</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.968235670728195</v>
+        <v>2.871102630690166</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.982706809389761</v>
+        <v>-3.29570103710164</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.333966837893771</v>
+        <v>1.208769146809019</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6309422786825405</v>
+        <v>0.4690538786191594</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.905971353172947</v>
+        <v>2.808838313134918</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.937868407781363</v>
+        <v>-3.250862635493242</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.355999901147758</v>
+        <v>1.230802210063007</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.63548571162741</v>
+        <v>0.4735973115640288</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.912795115550497</v>
+        <v>2.815662075512468</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.038627043538362</v>
+        <v>-3.35162127125024</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.319857386476037</v>
+        <v>1.194659695391286</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.5466601429004045</v>
+        <v>0.3847717428370234</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.863660713945372</v>
+        <v>2.766527673907343</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.994424206452461</v>
+        <v>-3.30741843416434</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.343418123838234</v>
+        <v>1.218220432753483</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.590862979986305</v>
+        <v>0.4289745799229239</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.896062018724749</v>
+        <v>2.798928978686721</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.031403234115905</v>
+        <v>-3.344397461827783</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.327036513242104</v>
+        <v>1.201838822157353</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.6278368817776355</v>
+        <v>0.4659484817142544</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.916656360268795</v>
+        <v>2.819523320230767</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.873111816576632</v>
+        <v>-3.186106044288511</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.441600845440853</v>
+        <v>1.316403154356102</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.6278368817776355</v>
+        <v>0.4659484817142544</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.967904125451835</v>
+        <v>2.870771085413806</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.665469812942156</v>
+        <v>-2.978464040654035</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.523098351488897</v>
+        <v>1.397900660404145</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.8354788854121117</v>
+        <v>0.6735904853487306</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.090930032226773</v>
+        <v>2.993796992188745</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.614437720219628</v>
+        <v>-2.927431947931507</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.538459416816178</v>
+        <v>1.413261725731427</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.8865109781346396</v>
+        <v>0.7246225780712585</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.116497516098561</v>
+        <v>3.019364476060532</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.549213539092422</v>
+        <v>-2.862207766804301</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.581736493359765</v>
+        <v>1.456538802275014</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.9517351592618453</v>
+        <v>0.7898467591984641</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.172819428867589</v>
+        <v>3.07568638882956</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.511786519021288</v>
+        <v>-2.824780746733167</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.592668273687499</v>
+        <v>1.467470582602748</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.9569866972910269</v>
+        <v>0.7950982972276458</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.171931323984378</v>
+        <v>3.074798283946349</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.531898175055997</v>
+        <v>-2.844892402767875</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.585880403604856</v>
+        <v>1.460682712520105</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.9680140422884461</v>
+        <v>0.806125642225065</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.17980452331407</v>
+        <v>3.082671483276041</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.478153360628792</v>
+        <v>-2.79114758834067</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.767936100396949</v>
+        <v>1.642738409312197</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9780773517289081</v>
+        <v>0.816188951665527</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.346400279999558</v>
+        <v>3.249267239961529</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.45436179202265</v>
+        <v>-2.767356019734528</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.897565637057223</v>
+        <v>1.772367945972471</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.00186892033505</v>
+        <v>0.8399805202716693</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.480788130381061</v>
+        <v>3.383655090343032</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.428277707758842</v>
+        <v>-2.74127193547072</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.899707246776605</v>
+        <v>1.774509555691854</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.00186892033505</v>
+        <v>0.8399805202716693</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.47249610639492</v>
+        <v>3.375363066356891</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.350146526909895</v>
+        <v>-2.663140754621773</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.929152914699963</v>
+        <v>1.803955223615212</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.076045731218735</v>
+        <v>0.9141573311553538</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.51519538850891</v>
+        <v>3.418062348470881</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.341254065516612</v>
+        <v>-2.65424829322849</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.950264304984068</v>
+        <v>1.825066613899317</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.076045731218735</v>
+        <v>0.9141573311553538</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.532749794235701</v>
+        <v>3.435616754197672</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.50973018248649</v>
+        <v>-2.822724410198368</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.874728905600701</v>
+        <v>1.749531214515949</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.048097895502154</v>
+        <v>0.886209495438773</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.507836140210337</v>
+        <v>3.410703100172308</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.811930653624906</v>
+        <v>-2.124924881336785</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.135118414333196</v>
+        <v>2.009920723248444</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9777498361317436</v>
+        <v>0.8158614360683623</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.446897001775952</v>
+        <v>3.349763961737923</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.789209549941754</v>
+        <v>-2.102203777653632</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.134870878303361</v>
+        <v>2.00967318721861</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9777498361317436</v>
+        <v>0.8158614360683623</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.437561024272857</v>
+        <v>3.340427984234828</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.78748450665171</v>
+        <v>-2.100478734363588</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.294467021470548</v>
+        <v>2.169269330385797</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9794748794217873</v>
+        <v>0.817586479358406</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.597502176098052</v>
+        <v>3.500369136060023</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.942265513429966</v>
+        <v>-2.255259741141844</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.269632441252893</v>
+        <v>2.144434750168141</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9461072053673112</v>
+        <v>0.7842188053039298</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.614559394159013</v>
+        <v>3.517426354120984</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.890830180045306</v>
+        <v>-2.203824407757184</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.286881930596302</v>
+        <v>2.16168423951155</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.9975425387519707</v>
+        <v>0.8356541386885895</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.642095950179354</v>
+        <v>3.544962910141325</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.863878955718818</v>
+        <v>-2.176873183430696</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.307668573971638</v>
+        <v>2.182470882886887</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.01242288477969</v>
+        <v>0.8505344847163087</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.661030311440727</v>
+        <v>3.563897271402698</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.999831963775134</v>
+        <v>-2.312826191487012</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.437390502894071</v>
+        <v>2.31219281180932</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.01242288477969</v>
+        <v>0.8505344847163087</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.845133443585687</v>
+        <v>3.748000403547658</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.022240081580006</v>
+        <v>-2.335234309291884</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.420543950675116</v>
+        <v>2.295346259590365</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.01242288477969</v>
+        <v>0.8505344847163087</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.83725013848868</v>
+        <v>3.740117098450651</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.170245849059405</v>
+        <v>-2.483240076771284</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.363395643232993</v>
+        <v>2.238197952148242</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.9256958759161484</v>
+        <v>0.7638074758527672</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.787267932720192</v>
+        <v>3.690134892682163</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.179686774947935</v>
+        <v>-2.492681002659814</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.415872990599429</v>
+        <v>2.290675299514677</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.04812299345954</v>
+        <v>0.8862345933961586</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.916977920968074</v>
+        <v>3.819844880930045</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.178400011408379</v>
+        <v>-2.491394239120257</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.419278790560552</v>
+        <v>2.294081099475801</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.049409756999096</v>
+        <v>0.8875213569357152</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.920641073637109</v>
+        <v>3.82350803359908</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.17995706539767</v>
+        <v>-2.492951293109549</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.416767781858611</v>
+        <v>2.291570090773859</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.049409756999096</v>
+        <v>0.8875213569357152</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.918752886530884</v>
+        <v>3.821619846492855</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.187228950921135</v>
+        <v>-2.500223178633013</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.408679257252087</v>
+        <v>2.283481566167336</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.042137871475632</v>
+        <v>0.8802494714122504</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.909209984819667</v>
+        <v>3.812076944781639</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.185387931862884</v>
+        <v>-2.498382159574762</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.40784967508554</v>
+        <v>2.282651984000788</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.0434060981471</v>
+        <v>0.8815176980837188</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.908404931032701</v>
+        <v>3.811271890994672</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.192296637362564</v>
+        <v>-2.505290865074443</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.418159599751586</v>
+        <v>2.292961908666835</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.0434060981471</v>
+        <v>0.8815176980837188</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.92147833789862</v>
+        <v>3.824345297860591</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.193858280177424</v>
+        <v>-2.506852507889302</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.417534942625642</v>
+        <v>2.292337251540891</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.0434060981471</v>
+        <v>0.8815176980837188</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.92147833789862</v>
+        <v>3.824345297860591</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.221759067286897</v>
+        <v>-2.534753294998775</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.404898668908855</v>
+        <v>2.279700977824104</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.008809174004165</v>
+        <v>0.846920773940784</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.89924422453986</v>
+        <v>3.802111184501832</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.224792064799571</v>
+        <v>-2.537786292511449</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.400449913880984</v>
+        <v>2.275252222796233</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.005776176491491</v>
+        <v>0.8438877764281101</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.894188870009455</v>
+        <v>3.797055829971426</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.244853386076078</v>
+        <v>-2.557847613787956</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.459131344960885</v>
+        <v>2.333933653876134</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.9857148552149841</v>
+        <v>0.823826455151603</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.948858036834054</v>
+        <v>3.851724996796026</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.501574204070902</v>
+        <v>-2.81456843178278</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.496754736764803</v>
+        <v>2.371557045680051</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8773002810711693</v>
+        <v>0.7154118810077882</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.024121011349613</v>
+        <v>3.926987971311584</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.655560621847042</v>
+        <v>-2.968554849558921</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.504140438799986</v>
+        <v>2.378942747715235</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8773002810711693</v>
+        <v>0.7154118810077882</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.093101280495253</v>
+        <v>3.995968240457223</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.605038718019376</v>
+        <v>-2.918032945731255</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.510400402451173</v>
+        <v>2.385202711366422</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8773002810711693</v>
+        <v>0.7154118810077882</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.079152482615373</v>
+        <v>3.982019442577345</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.857513872027101</v>
+        <v>-3.17050809973898</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.421280829903498</v>
+        <v>2.296083138818746</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8773002810711693</v>
+        <v>0.7154118810077882</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.091022971670787</v>
+        <v>3.993889931632759</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.6740426963583</v>
+        <v>3.674042696358299</v>
       </c>
       <c r="C2020" t="n">
         <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.126986673948809</v>
+        <v>-3.439980901660688</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.314702243653758</v>
+        <v>2.189504552569007</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8773002810711693</v>
+        <v>0.7154118810077882</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.092233506189731</v>
+        <v>3.995100466151702</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.851213545447334</v>
+        <v>3.413319079995288</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.774430059950164</v>
+        <v>3.458840448021636</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.126986673948809</v>
+        <v>-3.439980901660688</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.314702243653758</v>
+        <v>2.189504552569007</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.8773002810711693</v>
+        <v>0.7154118810077882</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.767493856936531</v>
+        <v>3.451904245008004</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240710.xlsx
+++ b/tame_output/ON/bt/strategyON_20240710.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,27 +849,27 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>45.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.3%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.0%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.9%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.0%</t>
+          <t>-67.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.6%</t>
+          <t>452.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-505.6%</t>
+          <t>-501.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.3%</t>
+          <t>-155.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.5%</t>
+          <t>-139.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-24.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-100.8%</t>
+          <t>-38.4%</t>
         </is>
       </c>
     </row>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111295</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.617515458616743</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.627687845048876</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.622634115622736</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.614409891067262</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.614961764100363</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.544234455991729</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.54610793191633</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.541183640428053</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.54667493625872</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.558172138027259</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.396527858027912</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.519809382105439</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.500616837437029</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.506308399775975</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.505512321672476</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.503112283226793</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.499637002435038</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677218871373718</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678052200359852</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.582010952033977</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.584804573565458</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.585466921957117</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.584547398697227</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.650882952494048</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.453174954208175</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.52346518653035</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.538092922646394</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.536628903471065</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.535120521510994</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.53498338894643</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.529377183085021</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.535758940112825</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.54065131348755</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
         <v>2.527405985963422</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.531503688574051</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.535664628205129</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.541544230732966</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.539954231202214</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.591201996385253</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.589642700979506</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.584590929217776</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404852</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.601778333310481</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.597739305609762</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84516980899266</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.598996097941002</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.759553868962213</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957624</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.87966677818003</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.871374754193889</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896926</v>
       </c>
       <c r="C1994" t="n">
         <v>2.869567949777668</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.88712235550446</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.878977402909044</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.860247100096906</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>2.85091112259381</v>
@@ -47522,7 +47522,7 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.009817248444979</v>
@@ -47545,7 +47545,7 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644413</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.046895070938626</v>
@@ -47568,7 +47568,7 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799964</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.043570426928171</v>
@@ -47591,7 +47591,7 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.053576580572912</v>
@@ -47614,7 +47614,7 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.237679712717872</v>
@@ -47637,7 +47637,7 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714426</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.229796407620865</v>
@@ -47660,7 +47660,7 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.231850407170503</v>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161979</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.28810412489235</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321636</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.290995219437651</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347704</v>
+        <v>3.727898186347702</v>
       </c>
       <c r="C2008" t="n">
         <v>3.289107032331426</v>
@@ -47752,7 +47752,7 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887748</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.283927261934288</v>
@@ -47775,7 +47775,7 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343066</v>
+        <v>3.712897612343064</v>
       </c>
       <c r="C2010" t="n">
         <v>3.282361272144441</v>
@@ -47798,7 +47798,7 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647107</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.295434679010359</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763533</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.295434679010359</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392117</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.293958720137361</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172528</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.29072316411456</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971081</v>
+        <v>3.619362241971079</v>
       </c>
       <c r="C2015" t="n">
         <v>3.357429123705064</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199807</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
         <v>3.497740842706911</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622238</v>
+        <v>3.668303164622237</v>
       </c>
       <c r="C2017" t="n">
         <v>3.566721111852551</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808531</v>
+        <v>3.619937176808529</v>
       </c>
       <c r="C2018" t="n">
         <v>3.552772313972671</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994896</v>
+        <v>3.656346893994894</v>
       </c>
       <c r="C2019" t="n">
         <v>3.564642803028085</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358299</v>
+        <v>3.674042696358298</v>
       </c>
       <c r="C2020" t="n">
         <v>3.565853337547029</v>
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.413319079995288</v>
+        <v>3.413319079995286</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.458840448021636</v>
+        <v>3.569975079774351</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.439980901660688</v>
+        <v>-3.403593650956028</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.189504552569007</v>
+        <v>2.208181195078192</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7154118810077882</v>
+        <v>0.8433821609095286</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.451904245008004</v>
+        <v>4.076004376320068</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240710.xlsx
+++ b/tame_output/ON/bt/strategyON_20240710.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.1%</t>
+          <t>-71.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>95.3%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-49.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.7%</t>
+          <t>-67.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-501.9%</t>
+          <t>-493.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.6%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-35.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>481.0%</t>
+          <t>481.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.4%</t>
+          <t>-152.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-123.0%</t>
+          <t>-125.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-139.7%</t>
+          <t>-128.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-31.9%</t>
         </is>
       </c>
     </row>
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.742767969509496</v>
+        <v>-4.702141710712824</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.062919069624309</v>
+        <v>1.079169573142978</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.1381437722345013</v>
+        <v>-0.09751751343782861</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.877496418401154</v>
+        <v>2.901872173679158</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.670525401338302</v>
+        <v>-4.629899142541629</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.095745410727607</v>
+        <v>1.111995914246276</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.1381437722345013</v>
+        <v>-0.09751751343782861</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.881425732235974</v>
+        <v>2.905801487513978</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.617527079056914</v>
+        <v>-4.576900820260241</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.117623323557502</v>
+        <v>1.133873827076171</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.08280751323256247</v>
+        <v>-0.04218125443588977</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.915306071554478</v>
+        <v>2.939681826832481</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.508722193577187</v>
+        <v>-4.468095934780514</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.158143348969386</v>
+        <v>1.174393852488055</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.08280751323256247</v>
+        <v>-0.04218125443588977</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.912304142774471</v>
+        <v>2.936679898052475</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.288701395540176</v>
+        <v>-4.248075136743504</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.247730705194805</v>
+        <v>1.263981208713474</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.05841233183541777</v>
+        <v>0.09903859063209047</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.998615086825873</v>
+        <v>3.022990842103877</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.155833706476899</v>
+        <v>-4.115207447680226</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.316771963621939</v>
+        <v>1.333022467140608</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.05841233183541777</v>
+        <v>0.09903859063209047</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.014509269627696</v>
+        <v>3.0388850249057</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.0356606231124</v>
+        <v>-3.995034364315727</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.36598704140804</v>
+        <v>1.382237544926709</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.1785854151999167</v>
+        <v>0.2192116739965894</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.087758964086698</v>
+        <v>3.112134719364701</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.890988478012662</v>
+        <v>-3.85036221921599</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.433944002009375</v>
+        <v>1.450194505528044</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.3232575602996541</v>
+        <v>0.3638838190963268</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.18465035370798</v>
+        <v>3.209026108985984</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.950863305370355</v>
+        <v>-3.910237046573682</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.396031562467724</v>
+        <v>1.412282065986393</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.263382732941962</v>
+        <v>0.3040089917386347</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.134762948694791</v>
+        <v>3.159138703972794</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.831043074459517</v>
+        <v>-3.790416815662845</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.459248824066268</v>
+        <v>1.475499327584937</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.263382732941962</v>
+        <v>0.3040089917386347</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.150052117929</v>
+        <v>3.174427873207003</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.833512780921323</v>
+        <v>-3.792886522124651</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.365905140803987</v>
+        <v>1.382155644322656</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.2609130264801559</v>
+        <v>0.3015392852768286</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.056214493374357</v>
+        <v>3.080590248652361</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.901882967245333</v>
+        <v>-3.861256708448661</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.257818927759684</v>
+        <v>1.274069431278353</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.2701887255163708</v>
+        <v>0.3108149843130435</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.981041774281388</v>
+        <v>3.005417529559391</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.91567102009238</v>
+        <v>-3.875044761295707</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.242740415252757</v>
+        <v>1.258990918771426</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.2701887255163708</v>
+        <v>0.3108149843130435</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.971478482913279</v>
+        <v>2.995854238191282</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.946664179421085</v>
+        <v>-3.906037920624413</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.055052716561661</v>
+        <v>1.071303220080331</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.2701887255163708</v>
+        <v>0.3108149843130435</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.796188047953666</v>
+        <v>2.820563803231669</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.771189919628616</v>
+        <v>-3.790361812388523</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.129809652470437</v>
+        <v>1.122140895366474</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.2701887255163708</v>
+        <v>0.4264910925489332</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.800755279945454</v>
+        <v>2.894536700164991</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.882126172269865</v>
+        <v>-3.901298065029772</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.061177180175145</v>
+        <v>1.053508423071182</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.2701887255163708</v>
+        <v>0.4264910925489332</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.776497308706661</v>
+        <v>2.870278728926198</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.617515458616743</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.848462626797583</v>
+        <v>-3.86763451955749</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.077773983583963</v>
+        <v>1.07010522648</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.3038522709886526</v>
+        <v>0.460154638021215</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.799826821209935</v>
+        <v>2.893608241429472</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.627687845048876</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.78861000759386</v>
+        <v>-3.807781900353767</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.111887417697585</v>
+        <v>1.104218660593622</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.3038522709886526</v>
+        <v>0.460154638021215</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.809999207642067</v>
+        <v>2.903780627861605</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.622634115622736</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.702366544567482</v>
+        <v>-3.721538437327389</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.141331073481996</v>
+        <v>1.133662316378033</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.3038522709886526</v>
+        <v>0.460154638021215</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.804945478215928</v>
+        <v>2.898726898435465</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.614409891067262</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.747673363966462</v>
+        <v>-3.766845256726369</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.114984121166929</v>
+        <v>1.107315364062967</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.2630421079794218</v>
+        <v>0.4193444750119842</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.772235155854915</v>
+        <v>2.866016576074452</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.614961764100363</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.776706468668764</v>
+        <v>-3.795878361428671</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.10392275231911</v>
+        <v>1.096253995215148</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.2630421079794218</v>
+        <v>0.4193444750119842</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.772787028888017</v>
+        <v>2.866568449107554</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.544234455991729</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.683895987217904</v>
+        <v>-3.703067879977811</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.07031963679082</v>
+        <v>1.062650879686857</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.3558525894302812</v>
+        <v>0.5121549564628436</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.757746009649898</v>
+        <v>2.851527429869435</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.54610793191633</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.728285456547332</v>
+        <v>-3.747457349307239</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.054437324983649</v>
+        <v>1.046768567879687</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.3114631201008535</v>
+        <v>0.4677654871334159</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.732985803976842</v>
+        <v>2.826767224196379</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.541183640428053</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.615614238311082</v>
+        <v>-3.634786131070989</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.094581520789873</v>
+        <v>1.08691276368591</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.4241343383371037</v>
+        <v>0.5804367053696662</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.795664243430315</v>
+        <v>2.889445663649853</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.54667493625872</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.503237237128409</v>
+        <v>-3.522409129888316</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.145023617093609</v>
+        <v>1.137354859989646</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.4241343383371037</v>
+        <v>0.5804367053696662</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.801155539260982</v>
+        <v>2.89493695948052</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.558172138027259</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.531017635029762</v>
+        <v>-3.550189527789669</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.145408659701607</v>
+        <v>1.137739902597644</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3963539404357507</v>
+        <v>0.5526563074683131</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.79598450228871</v>
+        <v>2.889765922508247</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.396527858027912</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.614018916055041</v>
+        <v>-3.633190808814948</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9505638672921484</v>
+        <v>0.9428951101881855</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3777830559085769</v>
+        <v>0.5340854229411394</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.623197691573059</v>
+        <v>2.716979111792596</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.516677518747118</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.722632994498372</v>
+        <v>-3.741804887258279</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.027267896634021</v>
+        <v>1.019599139530059</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3777830559085769</v>
+        <v>0.5340854229411394</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.743347352292264</v>
+        <v>2.837128772511802</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.531190544849441</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.68722395625023</v>
+        <v>-3.706395849010137</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.055944538035602</v>
+        <v>1.048275780931639</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3777830559085769</v>
+        <v>0.5340854229411394</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.757860378394587</v>
+        <v>2.851641798614124</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.528609986191809</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.648840293692079</v>
+        <v>-3.668012186451985</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.068717444401231</v>
+        <v>1.061048687297268</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4161667184667281</v>
+        <v>0.5724690854992905</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.778310017271846</v>
+        <v>2.872091437491384</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.525339015037112</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.471723963656912</v>
+        <v>-3.490895856416819</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.1362930052606</v>
+        <v>1.128624248156637</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4161667184667281</v>
+        <v>0.5724690854992905</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.775039046117149</v>
+        <v>2.868820466336687</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.526022406799025</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.516816208490458</v>
+        <v>-3.535988101250365</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.118939499089094</v>
+        <v>1.111270741985132</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.3542706752973383</v>
+        <v>0.5105730423299008</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.738584811977428</v>
+        <v>2.832366232196966</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.519809382105439</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.33744078725169</v>
+        <v>-3.356612680011597</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.184476642891016</v>
+        <v>1.176807885787053</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.511047433468057</v>
+        <v>0.6673498005006194</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.826437842186274</v>
+        <v>2.920219262405811</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.500616837437029</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.382455000772297</v>
+        <v>-3.401626893532204</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.147278412814363</v>
+        <v>1.1396096557104</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4806985381534524</v>
+        <v>0.6370009051860148</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.789035960329101</v>
+        <v>2.882817380548638</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.506308399775975</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.649459511044732</v>
+        <v>-3.668631403804639</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.046168171044335</v>
+        <v>1.038499413940372</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2863355001105038</v>
+        <v>0.4426378671430662</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.678109699842278</v>
+        <v>2.771891120061815</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.505512321672476</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.750657292481905</v>
+        <v>-3.769829185241812</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.004892980365967</v>
+        <v>0.9972242232620041</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2179266865651847</v>
+        <v>0.3742290535977471</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.636268333611587</v>
+        <v>2.730049753831125</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.503112283226793</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.744146325867592</v>
+        <v>-3.763318218627499</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.005097328566009</v>
+        <v>0.9974285714620459</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2179266865651847</v>
+        <v>0.3742290535977471</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.633868295165904</v>
+        <v>2.727649715385442</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.499637002435038</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.725108198160295</v>
+        <v>-3.744280090920202</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.009237298857173</v>
+        <v>1.00156854175321</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1597430752339901</v>
+        <v>0.3160454422665525</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.595482847575432</v>
+        <v>2.689264267794969</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.677218871373718</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.756234829310913</v>
+        <v>-3.77540672207082</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.174368515335606</v>
+        <v>1.166699758231643</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1597430752339901</v>
+        <v>0.3160454422665525</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.773064716514113</v>
+        <v>2.86684613673365</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
         <v>2.678052200359852</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.77010159064483</v>
+        <v>-3.789273483404737</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.169655139788172</v>
+        <v>1.16198638268421</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1218851585001672</v>
+        <v>0.2781875255327296</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.751183295459953</v>
+        <v>2.84496471567949</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
         <v>2.684060730756778</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.7252974191049</v>
+        <v>-3.744469311864807</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.19358533880107</v>
+        <v>1.185916581697108</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1218851585001672</v>
+        <v>0.2781875255327296</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.757191825856879</v>
+        <v>2.850973246076416</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.582010952033977</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.577554448869898</v>
+        <v>-3.596726341629805</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.150632748172271</v>
+        <v>1.142963991068308</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.2896925157350503</v>
+        <v>0.4459948827676127</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.755826461475008</v>
+        <v>2.849607881694545</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.584804573565458</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.679569131401119</v>
+        <v>-3.698741024161026</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.112620496691263</v>
+        <v>1.104951739587301</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.2896925157350503</v>
+        <v>0.4459948827676127</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.758620083006489</v>
+        <v>2.852401503226026</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
         <v>2.585466921957117</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.673416425348335</v>
+        <v>-3.692588318108242</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.115743927504036</v>
+        <v>1.108075170400073</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2958452217878346</v>
+        <v>0.452147588820397</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.762974055029818</v>
+        <v>2.856755475249355</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.584547398697227</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.690225723498836</v>
+        <v>-3.709397616258743</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.108100684983945</v>
+        <v>1.100431927879982</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.279035923637333</v>
+        <v>0.4353382906698954</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.751968952879627</v>
+        <v>2.845750373099164</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>2.650882952494048</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.627927724722714</v>
+        <v>-3.647099617482621</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.199355438291215</v>
+        <v>1.191686681187252</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.279035923637333</v>
+        <v>0.4353382906698954</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.818304506676448</v>
+        <v>2.912085926895985</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.453174954208175</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.426137527057556</v>
+        <v>-3.445309419817463</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.082363519071405</v>
+        <v>1.074694761967442</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.4770541158064874</v>
+        <v>0.6333564828390498</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.739407423692068</v>
+        <v>2.833188843911605</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
         <v>2.52346518653035</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.35275942996882</v>
+        <v>-3.371931322728727</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.182004990229075</v>
+        <v>1.174336233125112</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5504322128952239</v>
+        <v>0.7067345799277863</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.853724514267485</v>
+        <v>2.947505934487022</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
         <v>2.538092922646394</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.450499974593794</v>
+        <v>-3.469671867353701</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.157536508495129</v>
+        <v>1.149867751391166</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5345429347622437</v>
+        <v>0.6908453017948062</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.85881868350374</v>
+        <v>2.952600103723278</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.536628903471065</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.626837734716724</v>
+        <v>-3.64600962747663</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.085537385270629</v>
+        <v>1.077868628166666</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3582051746393143</v>
+        <v>0.5145075416718767</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.751552008254654</v>
+        <v>2.845333428474192</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.535120521510994</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.550415688284797</v>
+        <v>-3.569587581044704</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.114597821883328</v>
+        <v>1.106929064779365</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3582051746393143</v>
+        <v>0.5145075416718767</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.750043626294583</v>
+        <v>2.84382504651412</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.53498338894643</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.506042556646228</v>
+        <v>-3.525214449406135</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.132209941974192</v>
+        <v>1.124541184870229</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.4025783062778829</v>
+        <v>0.5588806733104453</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.77653037271316</v>
+        <v>2.870311792932698</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
         <v>2.529377183085021</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.383208335759061</v>
+        <v>-3.402380228518968</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.175737424467649</v>
+        <v>1.168068667363686</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.4025783062778829</v>
+        <v>0.5588806733104453</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.770924166851751</v>
+        <v>2.864705587071288</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
         <v>2.535758940112825</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.335552605198005</v>
+        <v>-3.354724497957912</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.201181473719876</v>
+        <v>1.193512716615913</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4502340368389385</v>
+        <v>0.606536403871501</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.805899362216189</v>
+        <v>2.899680782435726</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.54065131348755</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.235034446699251</v>
+        <v>-3.254206339459158</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.246281110494103</v>
+        <v>1.23861235339014</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.550752195337693</v>
+        <v>0.7070545623702555</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.871102630690166</v>
+        <v>2.964884050909704</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.527405985963422</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.29570103710164</v>
+        <v>-3.314872929861547</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.208769146809019</v>
+        <v>1.201100389705057</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.4690538786191594</v>
+        <v>0.6253562456517219</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.808838313134918</v>
+        <v>2.902619733354456</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.531503688574051</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.250862635493242</v>
+        <v>-3.270034528253149</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.230802210063007</v>
+        <v>1.223133452959044</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.4735973115640288</v>
+        <v>0.6298996785965914</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.815662075512468</v>
+        <v>2.909443495732006</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
         <v>2.535664628205129</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.35162127125024</v>
+        <v>-3.370793164010147</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.194659695391286</v>
+        <v>1.186990938287323</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.3847717428370234</v>
+        <v>0.5410741098695859</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.766527673907343</v>
+        <v>2.860309094126881</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.541544230732966</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.30741843416434</v>
+        <v>-3.326590326924247</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.218220432753483</v>
+        <v>1.21055167564952</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4289745799229239</v>
+        <v>0.5852769469554864</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.798928978686721</v>
+        <v>2.892710398906258</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.539954231202214</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.344397461827783</v>
+        <v>-3.36356935458769</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.201838822157353</v>
+        <v>1.19417006505339</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.4659484817142544</v>
+        <v>0.6222508487468169</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.819523320230767</v>
+        <v>2.913304740450304</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.591201996385253</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.186106044288511</v>
+        <v>-3.205277937048418</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.316403154356102</v>
+        <v>1.308734397252139</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.4659484817142544</v>
+        <v>0.6222508487468169</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.870771085413806</v>
+        <v>2.964552505633343</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.589642700979506</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.978464040654035</v>
+        <v>-2.997635933413942</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.397900660404145</v>
+        <v>1.390231903300183</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.6735904853487306</v>
+        <v>0.8298928523812931</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.993796992188745</v>
+        <v>3.087578412408282</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.584590929217776</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.927431947931507</v>
+        <v>-2.946603840691413</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.413261725731427</v>
+        <v>1.405592968627464</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7246225780712585</v>
+        <v>0.880924945103821</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.019364476060532</v>
+        <v>3.113145896280069</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.601778333310481</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.862207766804301</v>
+        <v>-2.801578568792034</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.456538802275014</v>
+        <v>1.48079048147992</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.7898467591984641</v>
+        <v>1.025950217003201</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.07568638882956</v>
+        <v>3.217348463512402</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.597739305609762</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.824780746733167</v>
+        <v>-2.7641515487209</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.467470582602748</v>
+        <v>1.491722261807654</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.7950982972276458</v>
+        <v>1.031201755032382</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.074798283946349</v>
+        <v>3.216460358629191</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.598996097941002</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.844892402767875</v>
+        <v>-2.784263204755609</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.460682712520105</v>
+        <v>1.484934391725011</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.806125642225065</v>
+        <v>1.042229100029801</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.082671483276041</v>
+        <v>3.224333557958883</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.759553868962213</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.79114758834067</v>
+        <v>-2.730518390328404</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.642738409312197</v>
+        <v>1.666990088517104</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.816188951665527</v>
+        <v>1.052292409470263</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.249267239961529</v>
+        <v>3.390929314644371</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957624</v>
       </c>
       <c r="C1992" t="n">
         <v>2.87966677818003</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.767356019734528</v>
+        <v>-2.706726821722262</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.772367945972471</v>
+        <v>1.796619625177378</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.8399805202716693</v>
+        <v>1.076083978076406</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.383655090343032</v>
+        <v>3.525317165025874</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>2.871374754193889</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.74127193547072</v>
+        <v>-2.680642737458454</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.774509555691854</v>
+        <v>1.79876123489676</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.8399805202716693</v>
+        <v>1.076083978076406</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.375363066356891</v>
+        <v>3.517025141039733</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896926</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.869567949777668</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.663140754621773</v>
+        <v>-2.602511556609507</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.803955223615212</v>
+        <v>1.828206902820119</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9141573311553538</v>
+        <v>1.15026078896009</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.418062348470881</v>
+        <v>3.559724423153723</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.88712235550446</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.65424829322849</v>
+        <v>-2.593619095216224</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.825066613899317</v>
+        <v>1.849318293104223</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9141573311553538</v>
+        <v>1.15026078896009</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.435616754197672</v>
+        <v>3.577278828880514</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.878977402909044</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.822724410198368</v>
+        <v>-2.762095212186102</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.749531214515949</v>
+        <v>1.773782893720856</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.886209495438773</v>
+        <v>1.12231295324351</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.410703100172308</v>
+        <v>3.55236517485515</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.860247100096906</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.124924881336785</v>
+        <v>-2.064295683324518</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.009920723248444</v>
+        <v>2.034172402453351</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.8158614360683623</v>
+        <v>1.051964893873099</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.349763961737923</v>
+        <v>3.491426036420765</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.85091112259381</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.102203777653632</v>
+        <v>-2.041574579641366</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.00967318721861</v>
+        <v>2.033924866423517</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.8158614360683623</v>
+        <v>1.051964893873099</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.340427984234828</v>
+        <v>3.48209005891767</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.009817248444979</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.100478734363588</v>
+        <v>-2.039849536351322</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.169269330385797</v>
+        <v>2.193521009590703</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.817586479358406</v>
+        <v>1.053689937163143</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.500369136060023</v>
+        <v>3.642031210742865</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644413</v>
       </c>
       <c r="C2000" t="n">
         <v>3.046895070938626</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.255259741141844</v>
+        <v>-2.194630543129577</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.144434750168141</v>
+        <v>2.168686429373048</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.7842188053039298</v>
+        <v>1.020322263108667</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.517426354120984</v>
+        <v>3.659088428803826</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799964</v>
       </c>
       <c r="C2001" t="n">
         <v>3.043570426928171</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.203824407757184</v>
+        <v>-2.143195209744917</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.16168423951155</v>
+        <v>2.185935918716457</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8356541386885895</v>
+        <v>1.071757596493326</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.544962910141325</v>
+        <v>3.686624984824167</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.053576580572912</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.176873183430696</v>
+        <v>-2.116243985418429</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.182470882886887</v>
+        <v>2.206722562091794</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8505344847163087</v>
+        <v>1.086637942521045</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.563897271402698</v>
+        <v>3.70555934608554</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.237679712717872</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.312826191487012</v>
+        <v>-2.252196993474746</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.31219281180932</v>
+        <v>2.336444491014227</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8505344847163087</v>
+        <v>1.086637942521045</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.748000403547658</v>
+        <v>3.8896624782305</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714426</v>
       </c>
       <c r="C2004" t="n">
         <v>3.229796407620865</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.335234309291884</v>
+        <v>-2.274605111279618</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.295346259590365</v>
+        <v>2.319597938795271</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8505344847163087</v>
+        <v>1.086637942521045</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.740117098450651</v>
+        <v>3.881779173133493</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.231850407170503</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.483240076771284</v>
+        <v>-2.422610878759017</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.238197952148242</v>
+        <v>2.262449631353149</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.7638074758527672</v>
+        <v>0.9999109336575038</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.690134892682163</v>
+        <v>3.831796967365005</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161979</v>
       </c>
       <c r="C2006" t="n">
         <v>3.28810412489235</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.492681002659814</v>
+        <v>-2.432051804647547</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.290675299514677</v>
+        <v>2.314926978719584</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.8862345933961586</v>
+        <v>1.122338051200895</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.819844880930045</v>
+        <v>3.961506955612887</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321636</v>
       </c>
       <c r="C2007" t="n">
         <v>3.290995219437651</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.491394239120257</v>
+        <v>-2.430765041107991</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.294081099475801</v>
+        <v>2.318332778680707</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8875213569357152</v>
+        <v>1.123624814740452</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.82350803359908</v>
+        <v>3.965170108281922</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347702</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
         <v>3.289107032331426</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.492951293109549</v>
+        <v>-2.432322095097282</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.291570090773859</v>
+        <v>2.315821769978766</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8875213569357152</v>
+        <v>1.123624814740452</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.821619846492855</v>
+        <v>3.963281921175697</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887748</v>
       </c>
       <c r="C2009" t="n">
         <v>3.283927261934288</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.500223178633013</v>
+        <v>-2.439593980620747</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.283481566167336</v>
+        <v>2.307733245372242</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.8802494714122504</v>
+        <v>1.116352929216987</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.812076944781639</v>
+        <v>3.95373901946448</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343064</v>
+        <v>3.712897612343066</v>
       </c>
       <c r="C2010" t="n">
         <v>3.282361272144441</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.498382159574762</v>
+        <v>-2.437752961562496</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.282651984000788</v>
+        <v>2.306903663205695</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8815176980837188</v>
+        <v>1.117621155888455</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.811271890994672</v>
+        <v>3.952933965677514</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647107</v>
       </c>
       <c r="C2011" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.505290865074443</v>
+        <v>-2.444661667062176</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.292961908666835</v>
+        <v>2.317213587871742</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8815176980837188</v>
+        <v>1.117621155888455</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.824345297860591</v>
+        <v>3.966007372543433</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.749896851763533</v>
       </c>
       <c r="C2012" t="n">
         <v>3.295434679010359</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.506852507889302</v>
+        <v>-2.446223309877036</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.292337251540891</v>
+        <v>2.316588930745798</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.8815176980837188</v>
+        <v>1.117621155888455</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.824345297860591</v>
+        <v>3.966007372543433</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392117</v>
       </c>
       <c r="C2013" t="n">
         <v>3.293958720137361</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.534753294998775</v>
+        <v>-2.474124096986509</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.279700977824104</v>
+        <v>2.303952657029011</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.846920773940784</v>
+        <v>1.083024231745521</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.802111184501832</v>
+        <v>3.943773259184674</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172528</v>
       </c>
       <c r="C2014" t="n">
         <v>3.29072316411456</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.537786292511449</v>
+        <v>-2.477157094499183</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.275252222796233</v>
+        <v>2.29950390200114</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8438877764281101</v>
+        <v>1.079991234232847</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.797055829971426</v>
+        <v>3.938717904654268</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971079</v>
+        <v>3.619362241971081</v>
       </c>
       <c r="C2015" t="n">
         <v>3.357429123705064</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.557847613787956</v>
+        <v>-2.49721841577569</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.333933653876134</v>
+        <v>2.358185333081041</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.823826455151603</v>
+        <v>1.05992991295634</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.851724996796026</v>
+        <v>3.993387071478868</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199807</v>
       </c>
       <c r="C2016" t="n">
         <v>3.497740842706911</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.81456843178278</v>
+        <v>-2.753939233770514</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.371557045680051</v>
+        <v>2.395808724884958</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.7154118810077882</v>
+        <v>0.9515153388125247</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.926987971311584</v>
+        <v>4.068650045994426</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622237</v>
+        <v>3.668303164622238</v>
       </c>
       <c r="C2017" t="n">
         <v>3.566721111852551</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.968554849558921</v>
+        <v>-2.907925651546654</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.378942747715235</v>
+        <v>2.403194426920142</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.7154118810077882</v>
+        <v>0.9515153388125247</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.995968240457223</v>
+        <v>4.137630315140066</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808529</v>
+        <v>3.619937176808531</v>
       </c>
       <c r="C2018" t="n">
         <v>3.552772313972671</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.918032945731255</v>
+        <v>-2.857403747718988</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.385202711366422</v>
+        <v>2.409454390571329</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.7154118810077882</v>
+        <v>0.9515153388125247</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.982019442577345</v>
+        <v>4.123681517260186</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994894</v>
+        <v>3.656346893994896</v>
       </c>
       <c r="C2019" t="n">
         <v>3.564642803028085</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.17050809973898</v>
+        <v>-3.109878901726713</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.296083138818746</v>
+        <v>2.320334818023653</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.7154118810077882</v>
+        <v>0.9515153388125247</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.993889931632759</v>
+        <v>4.1355520063156</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358298</v>
+        <v>3.6740426963583</v>
       </c>
       <c r="C2020" t="n">
         <v>3.565853337547029</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.439980901660688</v>
+        <v>-3.379351703648421</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.189504552569007</v>
+        <v>2.213756231773913</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.7154118810077882</v>
+        <v>0.9515153388125247</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.995100466151702</v>
+        <v>4.136762540834544</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.413319079995286</v>
+        <v>3.405958818737124</v>
       </c>
       <c r="C2021" t="n">
         <v>3.569975079774351</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.403593650956028</v>
+        <v>-3.320791294457891</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.208181195078192</v>
+        <v>2.241302137677447</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.8433821609095286</v>
+        <v>0.9515153388125247</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.076004376320068</v>
+        <v>4.140884283061865</v>
       </c>
     </row>
   </sheetData>
